--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -1,60 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3150EB98-85B1-4C3A-B1A5-9C09DBBE528F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1890" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="4">
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Encerrado!</t>
-  </si>
-  <si>
-    <t>Ordem pendente!</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -393,76 +420,345 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>5198569</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>685601364540</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>685601364299</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>685601378525</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>685601381337</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>685601381334</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>685601387728</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5198109</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5197922</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5198106</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5198103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5196637</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5198207</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5198105</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5198282</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5198152</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5198283</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5198284</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5198317</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5198814</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5198823</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5198868</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5198107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5197551</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5197684</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5197479</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5196638</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5198824</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>685601372068</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>685601377481</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>685601382481</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>685601383115</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>685601382620</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>685601390409</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>685601382993</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>685601382736</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>685601382526</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>685601382718</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>685601382385</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>685601381637</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>685601370707</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>685601376660</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>685601391132</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>685601390744</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>685601389211</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>685601385178</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>685601376288</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mao8ct\Desktop\PyAutomateSAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C9011A-5FFF-45C5-AFE4-2E7EF931CE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034F727-B03E-4924-9DBC-5AE63BEA1FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>OM</t>
   </si>
@@ -28,7 +28,28 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Ordem pendente!</t>
+    <t>5198988</t>
+  </si>
+  <si>
+    <t>5197545</t>
+  </si>
+  <si>
+    <t>685601370707</t>
+  </si>
+  <si>
+    <t>685601368954</t>
+  </si>
+  <si>
+    <t>685601392661</t>
+  </si>
+  <si>
+    <t>685601393506</t>
+  </si>
+  <si>
+    <t>685601369101</t>
+  </si>
+  <si>
+    <t>685601383435</t>
   </si>
 </sst>
 </file>
@@ -84,16 +105,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -397,11 +412,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -413,19 +428,43 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>685601382736</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>685601382718</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -1,78 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034F727-B03E-4924-9DBC-5AE63BEA1FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>5198988</t>
-  </si>
-  <si>
-    <t>5197545</t>
-  </si>
-  <si>
-    <t>685601370707</t>
-  </si>
-  <si>
-    <t>685601368954</t>
-  </si>
-  <si>
-    <t>685601392661</t>
-  </si>
-  <si>
-    <t>685601393506</t>
-  </si>
-  <si>
-    <t>685601369101</t>
-  </si>
-  <si>
-    <t>685601383435</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -411,60 +420,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5198988</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5197545</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>685601370707</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>685601368954</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>685601392661</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>685601393506</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>685601369101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>685601383435</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,84 +441,276 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>5198988</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5199092</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>5197545</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5198516</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>685601370707</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5197631</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>685601368954</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5198985</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>685601392661</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5199221</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>685601393506</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5199293</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>685601369101</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5199301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>685601383435</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5199319</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5198591</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5199004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5199093</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>685601382520</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>685601381892</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>685601383734</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>685601389216</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>685601393611</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>685601394568</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>685601381267</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>685601383321</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>685601392490</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>685601382993</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>685601383438</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>685601371492</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>685601378636</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>685601382462</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>685601341834</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>685601389365</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>685601378724</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>685601388510</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>685601375603</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>685601392665</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>685601394049</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>685601394297</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>685601362181</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -441,276 +441,344 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>5199092</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>5199092</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>5198516</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>5198516</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5197631</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>5197631</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5198985</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="n">
+        <v>5198985</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ordem pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5199221</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" t="n">
+        <v>5199221</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5199293</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>5199293</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5199301</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>5199301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>5199319</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="A9" t="n">
+        <v>5199319</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>5198591</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>5198591</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5199004</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>5199004</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5199093</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="n">
+        <v>5199093</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ordem pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>685601382520</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" t="n">
+        <v>685601382520</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>685601381892</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="n">
+        <v>685601381892</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>685601383734</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="n">
+        <v>685601383734</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>685601389216</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="n">
+        <v>685601389216</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>685601393611</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="n">
+        <v>685601393611</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>685601394568</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" t="n">
+        <v>685601394568</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>685601381267</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="A19" t="n">
+        <v>685601381267</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>685601383321</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="n">
+        <v>685601383321</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>685601392490</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="n">
+        <v>685601392490</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>685601382993</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="A22" t="n">
+        <v>685601382993</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>685601383438</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="A23" t="n">
+        <v>685601383438</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>685601371492</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="A24" t="n">
+        <v>685601371492</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>685601378636</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="A25" t="n">
+        <v>685601378636</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>685601382462</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="A26" t="n">
+        <v>685601382462</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>685601341834</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="A27" t="n">
+        <v>685601341834</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>685601389365</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="n">
+        <v>685601389365</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>685601378724</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="n">
+        <v>685601378724</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>685601388510</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="n">
+        <v>685601388510</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>685601375603</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>685601375603</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>685601392665</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="A32" t="n">
+        <v>685601392665</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>685601394049</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="A33" t="n">
+        <v>685601394049</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>685601394297</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="A34" t="n">
+        <v>685601394297</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>685601362181</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="A35" t="n">
+        <v>685601362181</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -1,99 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F91E7A-3A94-49DC-A1E7-7C12D16DAEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>5199381</t>
-  </si>
-  <si>
-    <t>5199432</t>
-  </si>
-  <si>
-    <t>5199215</t>
-  </si>
-  <si>
-    <t>5199375</t>
-  </si>
-  <si>
-    <t>5199559</t>
-  </si>
-  <si>
-    <t>5199499</t>
-  </si>
-  <si>
-    <t>685601394047</t>
-  </si>
-  <si>
-    <t>685601388510</t>
-  </si>
-  <si>
-    <t>685601394884</t>
-  </si>
-  <si>
-    <t>685601392787</t>
-  </si>
-  <si>
-    <t>685601393494</t>
-  </si>
-  <si>
-    <t>685601394137</t>
-  </si>
-  <si>
-    <t>685601385225</t>
-  </si>
-  <si>
-    <t>685601387918</t>
-  </si>
-  <si>
-    <t>685601387827</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -108,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -432,95 +420,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5199381</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5199432</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5199215</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5199375</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5199559</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5199499</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>685601394047</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>685601388510</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>685601394884</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>685601392787</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>685601393494</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>685601394137</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>685601385225</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>685601387918</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>685601387827</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -1,37 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6065D6F4-23AB-45D5-8FDE-EDD53986221C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>5198584</t>
+  </si>
+  <si>
+    <t>5199334</t>
+  </si>
+  <si>
+    <t>5198364</t>
+  </si>
+  <si>
+    <t>5198702</t>
+  </si>
+  <si>
+    <t>5198276</t>
+  </si>
+  <si>
+    <t>5198796</t>
+  </si>
+  <si>
+    <t>5199332</t>
+  </si>
+  <si>
+    <t>5199043</t>
+  </si>
+  <si>
+    <t>5198618</t>
+  </si>
+  <si>
+    <t>685601389042</t>
+  </si>
+  <si>
+    <t>685601388798</t>
+  </si>
+  <si>
+    <t>685601381888</t>
+  </si>
+  <si>
+    <t>685601387831</t>
+  </si>
+  <si>
+    <t>685601397096</t>
+  </si>
+  <si>
+    <t>685601387830</t>
+  </si>
+  <si>
+    <t>685601396165</t>
+  </si>
+  <si>
+    <t>685601381337</t>
+  </si>
+  <si>
+    <t>685601386361</t>
+  </si>
+  <si>
+    <t>685601387361</t>
+  </si>
+  <si>
+    <t>685601378479</t>
+  </si>
+  <si>
+    <t>685601389355</t>
+  </si>
+  <si>
+    <t>685601384990</t>
+  </si>
+  <si>
+    <t>685601383725</t>
+  </si>
+  <si>
+    <t>685601386901</t>
+  </si>
+  <si>
+    <t>685601381189</t>
+  </si>
+  <si>
+    <t>685601382521</t>
+  </si>
+  <si>
+    <t>685601389683</t>
+  </si>
+  <si>
+    <t>685601387289</t>
+  </si>
+  <si>
+    <t>685601387332</t>
+  </si>
+  <si>
+    <t>685601387786</t>
+  </si>
+  <si>
+    <t>685601386899</t>
+  </si>
+  <si>
+    <t>685601388871</t>
+  </si>
+  <si>
+    <t>685601384992</t>
+  </si>
+  <si>
+    <t>685601381682</t>
+  </si>
+  <si>
+    <t>685601371261</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +168,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,174 +492,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OM</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>5199381</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5199432</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5199215</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5199375</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5199559</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5199499</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>685601394047</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>685601388510</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>685601394884</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>685601392787</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>685601393494</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>685601394137</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>685601385225</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>685601387918</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>685601387827</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88C86C8-F95C-4DCD-8F98-647D63A75907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F75230-4356-4E9C-8A9A-889658D43FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>OM</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>5199522</t>
+  </si>
+  <si>
+    <t>5200130</t>
+  </si>
+  <si>
+    <t>5200512</t>
+  </si>
+  <si>
+    <t>5200524</t>
+  </si>
+  <si>
+    <t>5195516</t>
+  </si>
+  <si>
+    <t>5200063</t>
+  </si>
+  <si>
+    <t>5199322</t>
+  </si>
+  <si>
+    <t>5200068</t>
+  </si>
+  <si>
+    <t>685601400730</t>
+  </si>
+  <si>
+    <t>685601364220</t>
+  </si>
+  <si>
+    <t>685601387158</t>
+  </si>
+  <si>
+    <t>685601388768</t>
+  </si>
+  <si>
+    <t>685601387160</t>
+  </si>
+  <si>
+    <t>685601282237</t>
+  </si>
+  <si>
+    <t>685601402367</t>
+  </si>
+  <si>
+    <t>685601400817</t>
+  </si>
+  <si>
+    <t>685601400846</t>
+  </si>
+  <si>
+    <t>685601395669</t>
+  </si>
+  <si>
+    <t>685601400844</t>
+  </si>
+  <si>
+    <t>685601396166</t>
+  </si>
+  <si>
+    <t>685601388401</t>
   </si>
   <si>
     <t>5199327</t>
@@ -445,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -502,57 +565,162 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -1,61 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B14257-0BA1-49C9-8745-8EE37AA3FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -70,52 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,87 +420,385 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>5197572</v>
-      </c>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>685601355769</v>
-      </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>685601364160</v>
-      </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>685601381667</v>
-      </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>685601355769</v>
-      </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>685601381337</v>
-      </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>685601381334</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>685601382736</v>
-      </c>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>685601382718</v>
-      </c>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>5198985</v>
-      </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>5199093</v>
-      </c>
-      <c r="B12" s="2"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5199787</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5200014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5200306</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5200305</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5200138</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5200106</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5200160</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5200226</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5200179</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5200112</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5198091</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5200744</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5200452</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>685601401602</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>685601403471</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>685601403835</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>685601401311</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>685601397397</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>685601396692</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>685601397200</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>685601403832</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>685601400663</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>685601392573</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>685601400376</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>685601401209</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>685601382522</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>685601403583</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>685601385222</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>685601366315</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>685601392342</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>685601396398</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>685601396751</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>685601396752</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>685601381335</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>685601390226</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>355378</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>685601388256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>685601400209</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>685601388256</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>685601389525</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>685601400329</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>685601400328</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>685601400327</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>685601400325</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>685601405585</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D0AA88-53C4-46D0-B828-A31B6934E68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56773EEE-3A73-45AF-BD04-9F34B484CD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$3</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>OM</t>
   </si>
@@ -31,7 +28,85 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Ordem pendente!</t>
+    <t>5201056</t>
+  </si>
+  <si>
+    <t>5200586</t>
+  </si>
+  <si>
+    <t>5200255</t>
+  </si>
+  <si>
+    <t>5201009</t>
+  </si>
+  <si>
+    <t>5201030</t>
+  </si>
+  <si>
+    <t>685601397167</t>
+  </si>
+  <si>
+    <t>685601398084</t>
+  </si>
+  <si>
+    <t>685601397982</t>
+  </si>
+  <si>
+    <t>685601401166</t>
+  </si>
+  <si>
+    <t>685601401222</t>
+  </si>
+  <si>
+    <t>685601402080</t>
+  </si>
+  <si>
+    <t>685601399885</t>
+  </si>
+  <si>
+    <t>685601400376</t>
+  </si>
+  <si>
+    <t>685601395621</t>
+  </si>
+  <si>
+    <t>685601384622</t>
+  </si>
+  <si>
+    <t>685601395623</t>
+  </si>
+  <si>
+    <t>685601395940</t>
+  </si>
+  <si>
+    <t>685601397888</t>
+  </si>
+  <si>
+    <t>685601397886</t>
+  </si>
+  <si>
+    <t>685601397887</t>
+  </si>
+  <si>
+    <t>685601401337</t>
+  </si>
+  <si>
+    <t>685601397889</t>
+  </si>
+  <si>
+    <t>685601400303</t>
+  </si>
+  <si>
+    <t>685601398072</t>
+  </si>
+  <si>
+    <t>685601392570</t>
+  </si>
+  <si>
+    <t>685601392571</t>
+  </si>
+  <si>
+    <t>685601397317</t>
   </si>
 </sst>
 </file>
@@ -87,13 +162,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -397,11 +469,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -413,19 +485,143 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>685601400376</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>685601385222</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56773EEE-3A73-45AF-BD04-9F34B484CD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58180B02-20AB-485C-BF6E-87C86DD21565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>OM</t>
   </si>
@@ -28,85 +28,82 @@
     <t>Status</t>
   </si>
   <si>
-    <t>5201056</t>
-  </si>
-  <si>
-    <t>5200586</t>
-  </si>
-  <si>
-    <t>5200255</t>
-  </si>
-  <si>
-    <t>5201009</t>
-  </si>
-  <si>
-    <t>5201030</t>
-  </si>
-  <si>
-    <t>685601397167</t>
-  </si>
-  <si>
-    <t>685601398084</t>
-  </si>
-  <si>
-    <t>685601397982</t>
-  </si>
-  <si>
-    <t>685601401166</t>
-  </si>
-  <si>
-    <t>685601401222</t>
-  </si>
-  <si>
-    <t>685601402080</t>
-  </si>
-  <si>
-    <t>685601399885</t>
-  </si>
-  <si>
-    <t>685601400376</t>
-  </si>
-  <si>
-    <t>685601395621</t>
-  </si>
-  <si>
-    <t>685601384622</t>
-  </si>
-  <si>
-    <t>685601395623</t>
-  </si>
-  <si>
-    <t>685601395940</t>
-  </si>
-  <si>
-    <t>685601397888</t>
-  </si>
-  <si>
-    <t>685601397886</t>
-  </si>
-  <si>
-    <t>685601397887</t>
-  </si>
-  <si>
-    <t>685601401337</t>
-  </si>
-  <si>
-    <t>685601397889</t>
-  </si>
-  <si>
-    <t>685601400303</t>
-  </si>
-  <si>
-    <t>685601398072</t>
-  </si>
-  <si>
-    <t>685601392570</t>
-  </si>
-  <si>
-    <t>685601392571</t>
-  </si>
-  <si>
-    <t>685601397317</t>
+    <t>5201308</t>
+  </si>
+  <si>
+    <t>5201242</t>
+  </si>
+  <si>
+    <t>5201334</t>
+  </si>
+  <si>
+    <t>5199996</t>
+  </si>
+  <si>
+    <t>5199516</t>
+  </si>
+  <si>
+    <t>5200867</t>
+  </si>
+  <si>
+    <t>5201246</t>
+  </si>
+  <si>
+    <t>685601407529</t>
+  </si>
+  <si>
+    <t>685601405624</t>
+  </si>
+  <si>
+    <t>685601402088</t>
+  </si>
+  <si>
+    <t>685601408408</t>
+  </si>
+  <si>
+    <t>685601401970</t>
+  </si>
+  <si>
+    <t>685601402320</t>
+  </si>
+  <si>
+    <t>685601402159</t>
+  </si>
+  <si>
+    <t>685601400215</t>
+  </si>
+  <si>
+    <t>685601407530</t>
+  </si>
+  <si>
+    <t>685601398382</t>
+  </si>
+  <si>
+    <t>685601402749</t>
+  </si>
+  <si>
+    <t>685601401165</t>
+  </si>
+  <si>
+    <t>685601401952</t>
+  </si>
+  <si>
+    <t>685601403443</t>
+  </si>
+  <si>
+    <t>685601401620</t>
+  </si>
+  <si>
+    <t>685601349301</t>
+  </si>
+  <si>
+    <t>685601405463</t>
+  </si>
+  <si>
+    <t>685601403833</t>
+  </si>
+  <si>
+    <t>685601401623</t>
   </si>
 </sst>
 </file>
@@ -469,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -614,16 +611,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58180B02-20AB-485C-BF6E-87C86DD21565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8063BC16-5CE7-4670-8383-C43F2C1A23A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$7</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
   <si>
     <t>OM</t>
   </si>
@@ -28,82 +31,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>5201308</t>
-  </si>
-  <si>
-    <t>5201242</t>
-  </si>
-  <si>
-    <t>5201334</t>
-  </si>
-  <si>
-    <t>5199996</t>
-  </si>
-  <si>
-    <t>5199516</t>
-  </si>
-  <si>
-    <t>5200867</t>
-  </si>
-  <si>
-    <t>5201246</t>
-  </si>
-  <si>
-    <t>685601407529</t>
-  </si>
-  <si>
-    <t>685601405624</t>
-  </si>
-  <si>
-    <t>685601402088</t>
-  </si>
-  <si>
-    <t>685601408408</t>
-  </si>
-  <si>
-    <t>685601401970</t>
-  </si>
-  <si>
-    <t>685601402320</t>
-  </si>
-  <si>
-    <t>685601402159</t>
-  </si>
-  <si>
-    <t>685601400215</t>
-  </si>
-  <si>
-    <t>685601407530</t>
-  </si>
-  <si>
-    <t>685601398382</t>
-  </si>
-  <si>
-    <t>685601402749</t>
-  </si>
-  <si>
-    <t>685601401165</t>
-  </si>
-  <si>
-    <t>685601401952</t>
-  </si>
-  <si>
-    <t>685601403443</t>
-  </si>
-  <si>
-    <t>685601401620</t>
-  </si>
-  <si>
-    <t>685601349301</t>
-  </si>
-  <si>
-    <t>685601405463</t>
-  </si>
-  <si>
-    <t>685601403833</t>
-  </si>
-  <si>
-    <t>685601401623</t>
+    <t>Ordem pendente!</t>
   </si>
 </sst>
 </file>
@@ -159,10 +87,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,11 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,133 +413,51 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2">
+        <v>5199996</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
+      <c r="A3" s="2">
+        <v>685601402088</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
+      <c r="A4" s="2">
+        <v>685601402159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
+      <c r="A5" s="2">
+        <v>685601398382</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
+      <c r="A6" s="2">
+        <v>685601401165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
+      <c r="A7" s="2">
+        <v>685601401952</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8063BC16-5CE7-4670-8383-C43F2C1A23A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013DC658-D6ED-4799-90A4-8DDD0E93C413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$7</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentManualCount="28"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>OM</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Ordem pendente!</t>
   </si>
 </sst>
 </file>
@@ -92,7 +89,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -397,11 +394,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -414,50 +411,3142 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>5199996</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+        <v>5194522</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>685601402088</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+        <v>5192921</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>685601402159</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
+        <v>5192890</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>685601398382</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
+        <v>5192836</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>685601401165</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
+        <v>5192923</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>685601401952</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
+        <v>5192980</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>5193017</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>5193045</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>5192776</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>5192751</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>5192558</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>5192548</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>5192472</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5192407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>5192403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>5192402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>5192398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>5194405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>5194213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>5194081</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>5193787</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>5193545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>5193367</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>5193260</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>5193256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>5193183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>5193100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>5192397</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>5191529</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>5191508</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>5191487</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>5191427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>5191317</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>5191251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>5191182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>5191159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>5191156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>5192365</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>5192333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>5192317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>5192163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>5192080</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>5192060</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>5192046</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>5191926</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>5191912</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>5191866</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>5191806</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>5191782</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>5191672</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>5191664</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>5191646</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>5191606</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>5197668</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>5197599</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>5197557</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>5197256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>5197032</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>5197031</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>5196998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>5196890</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>5196715</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>5196605</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>5196602</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>5198949</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>5198837</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>5198756</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>5198577</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>5198523</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>5198431</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>5198369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>5197989</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>5196541</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>5195611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>5195435</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>5195416</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>5195415</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>5195359</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>5195296</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>5195285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>5195117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>5194533</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>5196450</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>5196443</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>5196405</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>5196349</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>5196341</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>5196334</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>5196240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>5195998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>5195967</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>5195957</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>5195791</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>5185446</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>5185530</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>5185595</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>5184871</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>5184818</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>5184507</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>5184340</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>5184327</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>5184283</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>5184282</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>5186538</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>5186492</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>5186403</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>5186177</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>5185939</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>5185897</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>5185746</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>5182386</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>5182296</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>5181876</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>5181792</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>5181703</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>5181670</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>5181437</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>5180981</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>5180925</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>5184123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>5183689</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>5183684</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>5183552</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>5183330</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>5183238</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>5183237</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>5183122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>5183092</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>5182769</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>5189780</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>5189722</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>5189662</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>5189652</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>5189520</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>5189515</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>5189413</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>5189032</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>5188868</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>5188841</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>5190831</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>5190655</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>5190614</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>5190444</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>5190065</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>5190038</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>5187421</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>5187361</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>5187232</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>5187222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>5187166</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>5187149</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>5186850</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>5188463</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>5188355</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>5188319</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>5188255</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>5188198</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>5188192</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>5187953</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>5187877</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>5187759</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>5187619</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>5187585</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>5187538</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>5187537</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>5192968</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>5192651</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>5192401</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>5192313</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>5197502</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>5194650</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>5185481</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>5181121</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>5183699</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>5188728</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <v>5188721</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>5192448</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <v>5194809</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <v>5187048</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <v>5190918</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>5192492</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <v>5192406</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>5192399</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>5194277</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>5193851</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>5193720</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>5191414</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>5191345</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>5197373</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>5197368</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>5197166</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <v>5197104</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>5196542</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <v>5198889</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>5198540</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>5198145</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <v>5197990</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>5197820</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>5195596</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>5195261</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>5195162</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>5194878</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>5194821</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>5194720</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>5196413</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>5196218</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>5195864</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>5195787</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>5195659</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>5185573</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>5184883</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>5186358</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>5186352</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>5186311</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>5186171</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>5186100</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>5185954</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>5185754</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>5182405</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>5181728</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>5181433</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>5181427</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>5181232</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>5180876</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>5183454</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>5182872</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>5182832</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>5182762</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>5189808</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>5189663</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>5188809</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>5188704</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>5188662</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>5190913</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>5190908</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>5190705</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>5190267</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>5187444</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>5187336</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>5187326</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>5187253</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>5187208</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>5187151</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>5187010</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>5187007</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>5186866</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>5186864</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>5188362</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>5187954</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>5197600</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>5182053</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>5181608</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>5181432</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>5181431</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>5182601</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <v>5186949</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <v>5186872</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
+        <v>5188028</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <v>5198573</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="2">
+        <v>5186010</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>5192919</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
+        <v>5192915</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>5192920</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="2">
+        <v>5192914</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
+        <v>5192841</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="2">
+        <v>5192828</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
+        <v>5192949</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="2">
+        <v>5192952</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
+        <v>5192973</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="2">
+        <v>5192975</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
+        <v>5192998</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="2">
+        <v>5192795</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>5192793</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
+        <v>5192789</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
+        <v>5192404</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="2">
+        <v>5192400</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="2">
+        <v>5194404</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>5194343</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
+        <v>5194280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="2">
+        <v>5194245</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
+        <v>5194244</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="2">
+        <v>5194243</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
+        <v>5194147</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
+        <v>5194067</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
+        <v>5193929</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="2">
+        <v>5193837</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
+        <v>5193789</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
+        <v>5193786</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
+        <v>5193663</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="2">
+        <v>5193494</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>5193409</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="2">
+        <v>5193387</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
+        <v>5193385</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="2">
+        <v>5193363</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
+        <v>5193352</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="2">
+        <v>5193320</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
+        <v>5193288</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
+        <v>5193287</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
+        <v>5193247</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="2">
+        <v>5193226</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
+        <v>5193177</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="2">
+        <v>5193090</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
+        <v>5191531</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="2">
+        <v>5191522</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
+        <v>5191497</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
+        <v>5191494</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
+        <v>5191420</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="2">
+        <v>5191413</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>5191411</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="2">
+        <v>5191410</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
+        <v>5191364</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="2">
+        <v>5191358</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>5191299</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="2">
+        <v>5191286</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>5191285</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="2">
+        <v>5191283</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>5191274</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="2">
+        <v>5191249</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>5191222</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="2">
+        <v>5191165</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
+        <v>5191151</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="2">
+        <v>5191123</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
+        <v>5191087</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>5191081</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
+        <v>5191074</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="2">
+        <v>5191037</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
+        <v>5191025</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="2">
+        <v>5192253</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
+        <v>5192251</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="2">
+        <v>5192213</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>5192209</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="2">
+        <v>5192144</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
+        <v>5192126</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="2">
+        <v>5192008</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>5191986</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="2">
+        <v>5191946</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>5191935</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="2">
+        <v>5191882</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>5191870</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
+        <v>5191839</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>5191831</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
+        <v>5191783</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>5191759</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="2">
+        <v>5191740</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
+        <v>5191659</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="2">
+        <v>5191648</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
+        <v>5191607</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="2">
+        <v>5197686</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
+        <v>5197630</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="2">
+        <v>5197374</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>5197176</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="2">
+        <v>5197011</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="2">
+        <v>5197002</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="2">
+        <v>5196978</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="2">
+        <v>5196968</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="2">
+        <v>5196911</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
+        <v>5196829</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="2">
+        <v>5196814</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2">
+        <v>5196772</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="2">
+        <v>5196765</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="2">
+        <v>5196763</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="2">
+        <v>5196719</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
+        <v>5196640</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="2">
+        <v>5196628</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="2">
+        <v>5196599</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
+        <v>5196598</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="2">
+        <v>5196580</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="2">
+        <v>5198934</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
+        <v>5198845</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="2">
+        <v>5198636</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
+        <v>5198634</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
+        <v>5198620</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
+        <v>5198619</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" s="2">
+        <v>5198519</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>5198468</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="2">
+        <v>5198449</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="2">
+        <v>5198429</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="2">
+        <v>5198385</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="2">
+        <v>5198350</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="2">
+        <v>5198334</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="2">
+        <v>5198321</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="2">
+        <v>5198315</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="2">
+        <v>5198205</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="2">
+        <v>5198157</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="2">
+        <v>5198113</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="2">
+        <v>5198112</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="2">
+        <v>5198078</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="2">
+        <v>5197988</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="2">
+        <v>5197948</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="2">
+        <v>5197735</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="2">
+        <v>5197733</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="2">
+        <v>5197731</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="2">
+        <v>5195648</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="2">
+        <v>5195624</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="2">
+        <v>5195413</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="2">
+        <v>5195322</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="2">
+        <v>5195294</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="2">
+        <v>5195251</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="2">
+        <v>5195244</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="2">
+        <v>5195134</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="2">
+        <v>5195078</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="2">
+        <v>5195051</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="2">
+        <v>5195049</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="2">
+        <v>5194969</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="2">
+        <v>5194955</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="2">
+        <v>5194841</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="2">
+        <v>5194792</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="2">
+        <v>5194686</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="2">
+        <v>5194658</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="2">
+        <v>5194645</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="2">
+        <v>5194620</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" s="2">
+        <v>5194618</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" s="2">
+        <v>5196510</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="2">
+        <v>5196411</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="2">
+        <v>5196404</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="2">
+        <v>5196363</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="2">
+        <v>5196354</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="2">
+        <v>5196350</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="2">
+        <v>5196347</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="2">
+        <v>5196336</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="2">
+        <v>5196331</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="2">
+        <v>5196328</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="2">
+        <v>5196221</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="2">
+        <v>5196183</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="2">
+        <v>5196128</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="2">
+        <v>5196065</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="2">
+        <v>5196000</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="2">
+        <v>5195996</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="2">
+        <v>5195991</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="2">
+        <v>5195965</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="2">
+        <v>5195827</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="2">
+        <v>5195793</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="2">
+        <v>5195782</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="2">
+        <v>5195690</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="2">
+        <v>5195687</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="2">
+        <v>5185234</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="2">
+        <v>5185233</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="2">
+        <v>5185317</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="2">
+        <v>5185113</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="2">
+        <v>5185005</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="2">
+        <v>5185000</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="2">
+        <v>5184978</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="2">
+        <v>5184945</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="2">
+        <v>5185447</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="2">
+        <v>5185533</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="2">
+        <v>5185538</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="2">
+        <v>5185543</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449" s="2">
+        <v>5185579</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450" s="2">
+        <v>5185641</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451" s="2">
+        <v>5184934</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452" s="2">
+        <v>5184813</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453" s="2">
+        <v>5184811</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454" s="2">
+        <v>5184810</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455" s="2">
+        <v>5184755</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456" s="2">
+        <v>5184619</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457" s="2">
+        <v>5184500</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="2">
+        <v>5184432</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="2">
+        <v>5184329</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460" s="2">
+        <v>5184319</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461" s="2">
+        <v>5184274</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462" s="2">
+        <v>5184190</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463" s="2">
+        <v>5186680</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464" s="2">
+        <v>5186647</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="2">
+        <v>5186644</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="2">
+        <v>5186611</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="2">
+        <v>5186590</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468" s="2">
+        <v>5186557</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469" s="2">
+        <v>5186473</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470" s="2">
+        <v>5186462</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471" s="2">
+        <v>5186373</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472" s="2">
+        <v>5186354</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A473" s="2">
+        <v>5186333</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A474" s="2">
+        <v>5186281</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A475" s="2">
+        <v>5186235</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476" s="2">
+        <v>5186109</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A477" s="2">
+        <v>5186080</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A478" s="2">
+        <v>5186016</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479" s="2">
+        <v>5186014</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480" s="2">
+        <v>5185922</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481" s="2">
+        <v>5185921</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482" s="2">
+        <v>5185898</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483" s="2">
+        <v>5185835</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484" s="2">
+        <v>5185783</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485" s="2">
+        <v>5185722</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486" s="2">
+        <v>5185674</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487" s="2">
+        <v>5184175</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A488" s="2">
+        <v>5182144</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A489" s="2">
+        <v>5181953</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A490" s="2">
+        <v>5181951</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A491" s="2">
+        <v>5181875</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A492" s="2">
+        <v>5181874</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A493" s="2">
+        <v>5181866</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494" s="2">
+        <v>5181745</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A495" s="2">
+        <v>5181708</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A496" s="2">
+        <v>5181572</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A497" s="2">
+        <v>5181443</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A498" s="2">
+        <v>5181403</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A499" s="2">
+        <v>5181345</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A500" s="2">
+        <v>5181328</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A501" s="2">
+        <v>5181292</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A502" s="2">
+        <v>5181275</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A503" s="2">
+        <v>5181256</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A504" s="2">
+        <v>5180953</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A505" s="2">
+        <v>5180944</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A506" s="2">
+        <v>5180877</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A507" s="2">
+        <v>5184172</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A508" s="2">
+        <v>5184159</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A509" s="2">
+        <v>5183971</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A510" s="2">
+        <v>5183970</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A511" s="2">
+        <v>5183942</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A512" s="2">
+        <v>5183932</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A513" s="2">
+        <v>5183783</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A514" s="2">
+        <v>5183723</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A515" s="2">
+        <v>5183578</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A516" s="2">
+        <v>5183577</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A517" s="2">
+        <v>5183550</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A518" s="2">
+        <v>5183543</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A519" s="2">
+        <v>5183534</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A520" s="2">
+        <v>5183492</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A521" s="2">
+        <v>5183441</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A522" s="2">
+        <v>5183387</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A523" s="2">
+        <v>5183232</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A524" s="2">
+        <v>5183177</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A525" s="2">
+        <v>5183160</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A526" s="2">
+        <v>5183159</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A527" s="2">
+        <v>5183101</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A528" s="2">
+        <v>5182868</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A529" s="2">
+        <v>5182432</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A530" s="2">
+        <v>5189960</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A531" s="2">
+        <v>5189847</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A532" s="2">
+        <v>5189846</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A533" s="2">
+        <v>5189840</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A534" s="2">
+        <v>5189820</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A535" s="2">
+        <v>5189783</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A536" s="2">
+        <v>5189530</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A537" s="2">
+        <v>5189411</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A538" s="2">
+        <v>5189376</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A539" s="2">
+        <v>5189364</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A540" s="2">
+        <v>5189363</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A541" s="2">
+        <v>5189344</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A542" s="2">
+        <v>5189342</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A543" s="2">
+        <v>5189328</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A544" s="2">
+        <v>5189327</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A545" s="2">
+        <v>5189297</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A546" s="2">
+        <v>5188724</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A547" s="2">
+        <v>5188710</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A548" s="2">
+        <v>5188709</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A549" s="2">
+        <v>5188680</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A550" s="2">
+        <v>5188618</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A551" s="2">
+        <v>5188586</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A552" s="2">
+        <v>5191024</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A553" s="2">
+        <v>5190961</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A554" s="2">
+        <v>5190925</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A555" s="2">
+        <v>5190844</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A556" s="2">
+        <v>5190815</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A557" s="2">
+        <v>5190811</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A558" s="2">
+        <v>5190757</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A559" s="2">
+        <v>5190753</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A560" s="2">
+        <v>5190741</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A561" s="2">
+        <v>5190737</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A562" s="2">
+        <v>5190726</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A563" s="2">
+        <v>5190706</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A564" s="2">
+        <v>5190626</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A565" s="2">
+        <v>5190584</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A566" s="2">
+        <v>5190543</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A567" s="2">
+        <v>5190533</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A568" s="2">
+        <v>5190500</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A569" s="2">
+        <v>5190417</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A570" s="2">
+        <v>5190224</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A571" s="2">
+        <v>5190149</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A572" s="2">
+        <v>5190146</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A573" s="2">
+        <v>5190067</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A574" s="2">
+        <v>5190066</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A575" s="2">
+        <v>5190028</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A576" s="2">
+        <v>5189980</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A577" s="2">
+        <v>5188566</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A578" s="2">
+        <v>5187376</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A579" s="2">
+        <v>5187372</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A580" s="2">
+        <v>5187370</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A581" s="2">
+        <v>5187334</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A582" s="2">
+        <v>5187287</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A583" s="2">
+        <v>5187244</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A584" s="2">
+        <v>5187226</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A585" s="2">
+        <v>5187225</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A586" s="2">
+        <v>5187211</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A587" s="2">
+        <v>5187148</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A588" s="2">
+        <v>5187074</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A589" s="2">
+        <v>5187067</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A590" s="2">
+        <v>5187049</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A591" s="2">
+        <v>5186874</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A592" s="2">
+        <v>5186853</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A593" s="2">
+        <v>5186788</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A594" s="2">
+        <v>5186734</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A595" s="2">
+        <v>5188289</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A596" s="2">
+        <v>5188230</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A597" s="2">
+        <v>5188216</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A598" s="2">
+        <v>5188150</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A599" s="2">
+        <v>5188148</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A600" s="2">
+        <v>5188024</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A601" s="2">
+        <v>5187948</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A602" s="2">
+        <v>5187947</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A603" s="2">
+        <v>5187936</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A604" s="2">
+        <v>5187886</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A605" s="2">
+        <v>5187876</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A606" s="2">
+        <v>5187747</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A607" s="2">
+        <v>5187718</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A608" s="2">
+        <v>5187711</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A609" s="2">
+        <v>5187669</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A610" s="2">
+        <v>5187621</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A611" s="2">
+        <v>5187620</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A612" s="2">
+        <v>5187618</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A613" s="2">
+        <v>5187540</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A614" s="2">
+        <v>5187539</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A615" s="2">
+        <v>5187490</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A616" s="2">
+        <v>5187471</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A617" s="2">
+        <v>5187465</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A618" s="2">
+        <v>5191365</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A619" s="2">
+        <v>5192322</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A620" s="2">
+        <v>5192321</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A621" s="2">
+        <v>5191604</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A622" s="2">
+        <v>5191125</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A623" s="2">
+        <v>5197478</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A624" s="2">
+        <v>5194521</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A625" s="2">
+        <v>5190847</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A626" s="2">
+        <v>5190842</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A627" s="2">
+        <v>5190275</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A628" s="2">
+        <v>5186728</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A629" s="2">
+        <v>5186695</v>
       </c>
     </row>
   </sheetData>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013DC658-D6ED-4799-90A4-8DDD0E93C413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0430BA87-B1BF-4DF1-BAD4-77EB3BEFAE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$7</definedName>
-  </definedNames>
-  <calcPr calcId="0" concurrentManualCount="28"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -84,13 +81,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -410,3142 +404,2862 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>5194522</v>
+      <c r="A2">
+        <v>5197256</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>5192921</v>
+      <c r="A3">
+        <v>5197032</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>5192890</v>
+      <c r="A4">
+        <v>5197031</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>5192836</v>
+      <c r="A5">
+        <v>5196998</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5192923</v>
+      <c r="A6">
+        <v>5196890</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>5192980</v>
+      <c r="A7">
+        <v>5196715</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>5193017</v>
+      <c r="A8">
+        <v>5196605</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>5193045</v>
+      <c r="A9">
+        <v>5196602</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>5192776</v>
+      <c r="A10">
+        <v>5198949</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>5192751</v>
+      <c r="A11">
+        <v>5198837</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>5192558</v>
+      <c r="A12">
+        <v>5198756</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>5192548</v>
+      <c r="A13">
+        <v>5198577</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>5192472</v>
+      <c r="A14">
+        <v>5198523</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>5192407</v>
+      <c r="A15">
+        <v>5198431</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>5192403</v>
+      <c r="A16">
+        <v>5198369</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>5192402</v>
+      <c r="A17">
+        <v>5197989</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>5192398</v>
+      <c r="A18">
+        <v>5196541</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>5194405</v>
+      <c r="A19">
+        <v>5195611</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>5194213</v>
+      <c r="A20">
+        <v>5195435</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>5194081</v>
+      <c r="A21">
+        <v>5195416</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>5193787</v>
+      <c r="A22">
+        <v>5195415</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>5193545</v>
+      <c r="A23">
+        <v>5195359</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>5193367</v>
+      <c r="A24">
+        <v>5195296</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>5193260</v>
+      <c r="A25">
+        <v>5195285</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>5193256</v>
+      <c r="A26">
+        <v>5195117</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>5193183</v>
+      <c r="A27">
+        <v>5194533</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>5193100</v>
+      <c r="A28">
+        <v>5196450</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>5192397</v>
+      <c r="A29">
+        <v>5196443</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>5191529</v>
+      <c r="A30">
+        <v>5196405</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>5191508</v>
+      <c r="A31">
+        <v>5196349</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>5191487</v>
+      <c r="A32">
+        <v>5196341</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>5191427</v>
+      <c r="A33">
+        <v>5196334</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>5191317</v>
+      <c r="A34">
+        <v>5196240</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>5191251</v>
+      <c r="A35">
+        <v>5195998</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>5191182</v>
+      <c r="A36">
+        <v>5195967</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>5191159</v>
+      <c r="A37">
+        <v>5195957</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>5191156</v>
+      <c r="A38">
+        <v>5195791</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>5192365</v>
+      <c r="A39">
+        <v>5185446</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>5192333</v>
+      <c r="A40">
+        <v>5185530</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>5192317</v>
+      <c r="A41">
+        <v>5185595</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>5192163</v>
+      <c r="A42">
+        <v>5184871</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>5192080</v>
+      <c r="A43">
+        <v>5184818</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>5192060</v>
+      <c r="A44">
+        <v>5184507</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>5192046</v>
+      <c r="A45">
+        <v>5184340</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>5191926</v>
+      <c r="A46">
+        <v>5184327</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>5191912</v>
+      <c r="A47">
+        <v>5184283</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>5191866</v>
+      <c r="A48">
+        <v>5184282</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>5191806</v>
+      <c r="A49">
+        <v>5186538</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>5191782</v>
+      <c r="A50">
+        <v>5186492</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>5191672</v>
+      <c r="A51">
+        <v>5186403</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>5191664</v>
+      <c r="A52">
+        <v>5186177</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>5191646</v>
+      <c r="A53">
+        <v>5185939</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>5191606</v>
+      <c r="A54">
+        <v>5185897</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>5197668</v>
+      <c r="A55">
+        <v>5185746</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>5197599</v>
+      <c r="A56">
+        <v>5182386</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>5197557</v>
+      <c r="A57">
+        <v>5182296</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>5197256</v>
+      <c r="A58">
+        <v>5181876</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>5197032</v>
+      <c r="A59">
+        <v>5181792</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>5197031</v>
+      <c r="A60">
+        <v>5181703</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>5196998</v>
+      <c r="A61">
+        <v>5181670</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>5196890</v>
+      <c r="A62">
+        <v>5181437</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>5196715</v>
+      <c r="A63">
+        <v>5180981</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>5196605</v>
+      <c r="A64">
+        <v>5180925</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>5196602</v>
+      <c r="A65">
+        <v>5184123</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>5198949</v>
+      <c r="A66">
+        <v>5183689</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>5198837</v>
+      <c r="A67">
+        <v>5183684</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>5198756</v>
+      <c r="A68">
+        <v>5183552</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>5198577</v>
+      <c r="A69">
+        <v>5183330</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>5198523</v>
+      <c r="A70">
+        <v>5183238</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>5198431</v>
+      <c r="A71">
+        <v>5183237</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>5198369</v>
+      <c r="A72">
+        <v>5183122</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>5197989</v>
+      <c r="A73">
+        <v>5183092</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>5196541</v>
+      <c r="A74">
+        <v>5182769</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>5195611</v>
+      <c r="A75">
+        <v>5189780</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>5195435</v>
+      <c r="A76">
+        <v>5189722</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>5195416</v>
+      <c r="A77">
+        <v>5189662</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>5195415</v>
+      <c r="A78">
+        <v>5189652</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>5195359</v>
+      <c r="A79">
+        <v>5189520</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>5195296</v>
+      <c r="A80">
+        <v>5189515</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>5195285</v>
+      <c r="A81">
+        <v>5189413</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>5195117</v>
+      <c r="A82">
+        <v>5189032</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>5194533</v>
+      <c r="A83">
+        <v>5188868</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>5196450</v>
+      <c r="A84">
+        <v>5188841</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>5196443</v>
+      <c r="A85">
+        <v>5190831</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>5196405</v>
+      <c r="A86">
+        <v>5190655</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>5196349</v>
+      <c r="A87">
+        <v>5190614</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>5196341</v>
+      <c r="A88">
+        <v>5190444</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>5196334</v>
+      <c r="A89">
+        <v>5190065</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>5196240</v>
+      <c r="A90">
+        <v>5190038</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>5195998</v>
+      <c r="A91">
+        <v>5187421</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>5195967</v>
+      <c r="A92">
+        <v>5187361</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>5195957</v>
+      <c r="A93">
+        <v>5187232</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>5195791</v>
+      <c r="A94">
+        <v>5187222</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>5185446</v>
+      <c r="A95">
+        <v>5187166</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>5185530</v>
+      <c r="A96">
+        <v>5187149</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>5185595</v>
+      <c r="A97">
+        <v>5186850</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>5184871</v>
+      <c r="A98">
+        <v>5188463</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>5184818</v>
+      <c r="A99">
+        <v>5188355</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>5184507</v>
+      <c r="A100">
+        <v>5188319</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>5184340</v>
+      <c r="A101">
+        <v>5188255</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>5184327</v>
+      <c r="A102">
+        <v>5188198</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>5184283</v>
+      <c r="A103">
+        <v>5188192</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>5184282</v>
+      <c r="A104">
+        <v>5187953</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>5186538</v>
+      <c r="A105">
+        <v>5187877</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>5186492</v>
+      <c r="A106">
+        <v>5187759</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>5186403</v>
+      <c r="A107">
+        <v>5187619</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>5186177</v>
+      <c r="A108">
+        <v>5187585</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>5185939</v>
+      <c r="A109">
+        <v>5187538</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>5185897</v>
+      <c r="A110">
+        <v>5187537</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>5185746</v>
+      <c r="A111">
+        <v>5192968</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>5182386</v>
+      <c r="A112">
+        <v>5192651</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>5182296</v>
+      <c r="A113">
+        <v>5192401</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>5181876</v>
+      <c r="A114">
+        <v>5192313</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>5181792</v>
+      <c r="A115">
+        <v>5197502</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
-        <v>5181703</v>
+      <c r="A116">
+        <v>5194650</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
-        <v>5181670</v>
+      <c r="A117">
+        <v>5185481</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>5181437</v>
+      <c r="A118">
+        <v>5181121</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>5180981</v>
+      <c r="A119">
+        <v>5183699</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>5180925</v>
+      <c r="A120">
+        <v>5188728</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>5184123</v>
+      <c r="A121">
+        <v>5188721</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>5183689</v>
+      <c r="A122">
+        <v>5192448</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>5183684</v>
+      <c r="A123">
+        <v>5194809</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>5183552</v>
+      <c r="A124">
+        <v>5187048</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>5183330</v>
+      <c r="A125">
+        <v>5190918</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>5183238</v>
+      <c r="A126">
+        <v>5192492</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>5183237</v>
+      <c r="A127">
+        <v>5192406</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>5183122</v>
+      <c r="A128">
+        <v>5192399</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>5183092</v>
+      <c r="A129">
+        <v>5194277</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>5182769</v>
+      <c r="A130">
+        <v>5193851</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>5189780</v>
+      <c r="A131">
+        <v>5193720</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>5189722</v>
+      <c r="A132">
+        <v>5191414</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>5189662</v>
+      <c r="A133">
+        <v>5191345</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>5189652</v>
+      <c r="A134">
+        <v>5197373</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>5189520</v>
+      <c r="A135">
+        <v>5197368</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>5189515</v>
+      <c r="A136">
+        <v>5197166</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>5189413</v>
+      <c r="A137">
+        <v>5197104</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>5189032</v>
+      <c r="A138">
+        <v>5196542</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
-        <v>5188868</v>
+      <c r="A139">
+        <v>5198889</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>5188841</v>
+      <c r="A140">
+        <v>5198540</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
-        <v>5190831</v>
+      <c r="A141">
+        <v>5198145</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>5190655</v>
+      <c r="A142">
+        <v>5197990</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
-        <v>5190614</v>
+      <c r="A143">
+        <v>5197820</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
-        <v>5190444</v>
+      <c r="A144">
+        <v>5195596</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
-        <v>5190065</v>
+      <c r="A145">
+        <v>5195261</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
-        <v>5190038</v>
+      <c r="A146">
+        <v>5195162</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>5187421</v>
+      <c r="A147">
+        <v>5194878</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
-        <v>5187361</v>
+      <c r="A148">
+        <v>5194821</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
-        <v>5187232</v>
+      <c r="A149">
+        <v>5194720</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
-        <v>5187222</v>
+      <c r="A150">
+        <v>5196413</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
-        <v>5187166</v>
+      <c r="A151">
+        <v>5196218</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
-        <v>5187149</v>
+      <c r="A152">
+        <v>5195864</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
-        <v>5186850</v>
+      <c r="A153">
+        <v>5195787</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
-        <v>5188463</v>
+      <c r="A154">
+        <v>5195659</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>5188355</v>
+      <c r="A155">
+        <v>5185573</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>5188319</v>
+      <c r="A156">
+        <v>5184883</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
-        <v>5188255</v>
+      <c r="A157">
+        <v>5186358</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>5188198</v>
+      <c r="A158">
+        <v>5186352</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>5188192</v>
+      <c r="A159">
+        <v>5186311</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
-        <v>5187953</v>
+      <c r="A160">
+        <v>5186171</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
-        <v>5187877</v>
+      <c r="A161">
+        <v>5186100</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
-        <v>5187759</v>
+      <c r="A162">
+        <v>5185954</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
-        <v>5187619</v>
+      <c r="A163">
+        <v>5185754</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
-        <v>5187585</v>
+      <c r="A164">
+        <v>5182405</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
-        <v>5187538</v>
+      <c r="A165">
+        <v>5181728</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>5187537</v>
+      <c r="A166">
+        <v>5181433</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>5192968</v>
+      <c r="A167">
+        <v>5181427</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>5192651</v>
+      <c r="A168">
+        <v>5181232</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
-        <v>5192401</v>
+      <c r="A169">
+        <v>5180876</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>5192313</v>
+      <c r="A170">
+        <v>5183454</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>5197502</v>
+      <c r="A171">
+        <v>5182872</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>5194650</v>
+      <c r="A172">
+        <v>5182832</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>5185481</v>
+      <c r="A173">
+        <v>5182762</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>5181121</v>
+      <c r="A174">
+        <v>5189808</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>5183699</v>
+      <c r="A175">
+        <v>5189663</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
-        <v>5188728</v>
+      <c r="A176">
+        <v>5188809</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>5188721</v>
+      <c r="A177">
+        <v>5188704</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
-        <v>5192448</v>
+      <c r="A178">
+        <v>5188662</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
-        <v>5194809</v>
+      <c r="A179">
+        <v>5190913</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
-        <v>5187048</v>
+      <c r="A180">
+        <v>5190908</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
-        <v>5190918</v>
+      <c r="A181">
+        <v>5190705</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
-        <v>5192492</v>
+      <c r="A182">
+        <v>5190267</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
-        <v>5192406</v>
+      <c r="A183">
+        <v>5187444</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>5192399</v>
+      <c r="A184">
+        <v>5187336</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
-        <v>5194277</v>
+      <c r="A185">
+        <v>5187326</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>5193851</v>
+      <c r="A186">
+        <v>5187253</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>5193720</v>
+      <c r="A187">
+        <v>5187208</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
-        <v>5191414</v>
+      <c r="A188">
+        <v>5187151</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>5191345</v>
+      <c r="A189">
+        <v>5187010</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>5197373</v>
+      <c r="A190">
+        <v>5187007</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
-        <v>5197368</v>
+      <c r="A191">
+        <v>5186866</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
-        <v>5197166</v>
+      <c r="A192">
+        <v>5186864</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
-        <v>5197104</v>
+      <c r="A193">
+        <v>5188362</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
-        <v>5196542</v>
+      <c r="A194">
+        <v>5187954</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
-        <v>5198889</v>
+      <c r="A195">
+        <v>5197600</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
-        <v>5198540</v>
+      <c r="A196">
+        <v>5182053</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
-        <v>5198145</v>
+      <c r="A197">
+        <v>5181608</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
-        <v>5197990</v>
+      <c r="A198">
+        <v>5181432</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
-        <v>5197820</v>
+      <c r="A199">
+        <v>5181431</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
-        <v>5195596</v>
+      <c r="A200">
+        <v>5182601</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
-        <v>5195261</v>
+      <c r="A201">
+        <v>5186949</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
-        <v>5195162</v>
+      <c r="A202">
+        <v>5186872</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
-        <v>5194878</v>
+      <c r="A203">
+        <v>5188028</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
-        <v>5194821</v>
+      <c r="A204">
+        <v>5198573</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
-        <v>5194720</v>
+      <c r="A205">
+        <v>5186010</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
-        <v>5196413</v>
+      <c r="A206">
+        <v>5192919</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
-        <v>5196218</v>
+      <c r="A207">
+        <v>5192915</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
-        <v>5195864</v>
+      <c r="A208">
+        <v>5192920</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
-        <v>5195787</v>
+      <c r="A209">
+        <v>5192914</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" s="2">
-        <v>5195659</v>
+      <c r="A210">
+        <v>5192841</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
-        <v>5185573</v>
+      <c r="A211">
+        <v>5192828</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
-        <v>5184883</v>
+      <c r="A212">
+        <v>5192949</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="2">
-        <v>5186358</v>
+      <c r="A213">
+        <v>5192952</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" s="2">
-        <v>5186352</v>
+      <c r="A214">
+        <v>5192973</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
-        <v>5186311</v>
+      <c r="A215">
+        <v>5192975</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="2">
-        <v>5186171</v>
+      <c r="A216">
+        <v>5192998</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
-        <v>5186100</v>
+      <c r="A217">
+        <v>5192795</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
-        <v>5185954</v>
+      <c r="A218">
+        <v>5192793</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="2">
-        <v>5185754</v>
+      <c r="A219">
+        <v>5192789</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
-        <v>5182405</v>
+      <c r="A220">
+        <v>5192404</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
-        <v>5181728</v>
+      <c r="A221">
+        <v>5192400</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
-        <v>5181433</v>
+      <c r="A222">
+        <v>5194404</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
-        <v>5181427</v>
+      <c r="A223">
+        <v>5194343</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
-        <v>5181232</v>
+      <c r="A224">
+        <v>5194280</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
-        <v>5180876</v>
+      <c r="A225">
+        <v>5194245</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
-        <v>5183454</v>
+      <c r="A226">
+        <v>5194244</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
-        <v>5182872</v>
+      <c r="A227">
+        <v>5194243</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
-        <v>5182832</v>
+      <c r="A228">
+        <v>5194147</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
-        <v>5182762</v>
+      <c r="A229">
+        <v>5194067</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
-        <v>5189808</v>
+      <c r="A230">
+        <v>5193929</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
-        <v>5189663</v>
+      <c r="A231">
+        <v>5193837</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
-        <v>5188809</v>
+      <c r="A232">
+        <v>5193789</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
-        <v>5188704</v>
+      <c r="A233">
+        <v>5193786</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
-        <v>5188662</v>
+      <c r="A234">
+        <v>5193663</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
-        <v>5190913</v>
+      <c r="A235">
+        <v>5193494</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
-        <v>5190908</v>
+      <c r="A236">
+        <v>5193409</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
-        <v>5190705</v>
+      <c r="A237">
+        <v>5193387</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
-        <v>5190267</v>
+      <c r="A238">
+        <v>5193385</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
-        <v>5187444</v>
+      <c r="A239">
+        <v>5193363</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
-        <v>5187336</v>
+      <c r="A240">
+        <v>5193352</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
-        <v>5187326</v>
+      <c r="A241">
+        <v>5193320</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
-        <v>5187253</v>
+      <c r="A242">
+        <v>5193288</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="2">
-        <v>5187208</v>
+      <c r="A243">
+        <v>5193287</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
-        <v>5187151</v>
+      <c r="A244">
+        <v>5193247</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" s="2">
-        <v>5187010</v>
+      <c r="A245">
+        <v>5193226</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
-        <v>5187007</v>
+      <c r="A246">
+        <v>5193177</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" s="2">
-        <v>5186866</v>
+      <c r="A247">
+        <v>5193090</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
-        <v>5186864</v>
+      <c r="A248">
+        <v>5191531</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
-        <v>5188362</v>
+      <c r="A249">
+        <v>5191522</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
-        <v>5187954</v>
+      <c r="A250">
+        <v>5191497</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
-        <v>5197600</v>
+      <c r="A251">
+        <v>5191494</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
-        <v>5182053</v>
+      <c r="A252">
+        <v>5191420</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" s="2">
-        <v>5181608</v>
+      <c r="A253">
+        <v>5191413</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" s="2">
-        <v>5181432</v>
+      <c r="A254">
+        <v>5191411</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" s="2">
-        <v>5181431</v>
+      <c r="A255">
+        <v>5191410</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" s="2">
-        <v>5182601</v>
+      <c r="A256">
+        <v>5191364</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" s="2">
-        <v>5186949</v>
+      <c r="A257">
+        <v>5191358</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" s="2">
-        <v>5186872</v>
+      <c r="A258">
+        <v>5191299</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" s="2">
-        <v>5188028</v>
+      <c r="A259">
+        <v>5191286</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" s="2">
-        <v>5198573</v>
+      <c r="A260">
+        <v>5191285</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" s="2">
-        <v>5186010</v>
+      <c r="A261">
+        <v>5191283</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" s="2">
-        <v>5192919</v>
+      <c r="A262">
+        <v>5191274</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" s="2">
-        <v>5192915</v>
+      <c r="A263">
+        <v>5191249</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" s="2">
-        <v>5192920</v>
+      <c r="A264">
+        <v>5191222</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" s="2">
-        <v>5192914</v>
+      <c r="A265">
+        <v>5191165</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266" s="2">
-        <v>5192841</v>
+      <c r="A266">
+        <v>5191151</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267" s="2">
-        <v>5192828</v>
+      <c r="A267">
+        <v>5191123</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" s="2">
-        <v>5192949</v>
+      <c r="A268">
+        <v>5191087</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" s="2">
-        <v>5192952</v>
+      <c r="A269">
+        <v>5191081</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" s="2">
-        <v>5192973</v>
+      <c r="A270">
+        <v>5191074</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" s="2">
-        <v>5192975</v>
+      <c r="A271">
+        <v>5191037</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" s="2">
-        <v>5192998</v>
+      <c r="A272">
+        <v>5191025</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" s="2">
-        <v>5192795</v>
+      <c r="A273">
+        <v>5192253</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" s="2">
-        <v>5192793</v>
+      <c r="A274">
+        <v>5192251</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" s="2">
-        <v>5192789</v>
+      <c r="A275">
+        <v>5192213</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" s="2">
-        <v>5192404</v>
+      <c r="A276">
+        <v>5192209</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" s="2">
-        <v>5192400</v>
+      <c r="A277">
+        <v>5192144</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" s="2">
-        <v>5194404</v>
+      <c r="A278">
+        <v>5192126</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" s="2">
-        <v>5194343</v>
+      <c r="A279">
+        <v>5192008</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" s="2">
-        <v>5194280</v>
+      <c r="A280">
+        <v>5191986</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" s="2">
-        <v>5194245</v>
+      <c r="A281">
+        <v>5191946</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" s="2">
-        <v>5194244</v>
+      <c r="A282">
+        <v>5191935</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" s="2">
-        <v>5194243</v>
+      <c r="A283">
+        <v>5191882</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" s="2">
-        <v>5194147</v>
+      <c r="A284">
+        <v>5191870</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" s="2">
-        <v>5194067</v>
+      <c r="A285">
+        <v>5191839</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" s="2">
-        <v>5193929</v>
+      <c r="A286">
+        <v>5191831</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" s="2">
-        <v>5193837</v>
+      <c r="A287">
+        <v>5191783</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" s="2">
-        <v>5193789</v>
+      <c r="A288">
+        <v>5191759</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" s="2">
-        <v>5193786</v>
+      <c r="A289">
+        <v>5191740</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" s="2">
-        <v>5193663</v>
+      <c r="A290">
+        <v>5191659</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291" s="2">
-        <v>5193494</v>
+      <c r="A291">
+        <v>5191648</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" s="2">
-        <v>5193409</v>
+      <c r="A292">
+        <v>5191607</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293" s="2">
-        <v>5193387</v>
+      <c r="A293">
+        <v>5197686</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" s="2">
-        <v>5193385</v>
+      <c r="A294">
+        <v>5197630</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" s="2">
-        <v>5193363</v>
+      <c r="A295">
+        <v>5197374</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" s="2">
-        <v>5193352</v>
+      <c r="A296">
+        <v>5197176</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297" s="2">
-        <v>5193320</v>
+      <c r="A297">
+        <v>5197011</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298" s="2">
-        <v>5193288</v>
+      <c r="A298">
+        <v>5197002</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299" s="2">
-        <v>5193287</v>
+      <c r="A299">
+        <v>5196978</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" s="2">
-        <v>5193247</v>
+      <c r="A300">
+        <v>5196968</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" s="2">
-        <v>5193226</v>
+      <c r="A301">
+        <v>5196911</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302" s="2">
-        <v>5193177</v>
+      <c r="A302">
+        <v>5196829</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" s="2">
-        <v>5193090</v>
+      <c r="A303">
+        <v>5196814</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" s="2">
-        <v>5191531</v>
+      <c r="A304">
+        <v>5196772</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305" s="2">
-        <v>5191522</v>
+      <c r="A305">
+        <v>5196765</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" s="2">
-        <v>5191497</v>
+      <c r="A306">
+        <v>5196763</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" s="2">
-        <v>5191494</v>
+      <c r="A307">
+        <v>5196719</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" s="2">
-        <v>5191420</v>
+      <c r="A308">
+        <v>5196640</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309" s="2">
-        <v>5191413</v>
+      <c r="A309">
+        <v>5196628</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" s="2">
-        <v>5191411</v>
+      <c r="A310">
+        <v>5196599</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" s="2">
-        <v>5191410</v>
+      <c r="A311">
+        <v>5196598</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" s="2">
-        <v>5191364</v>
+      <c r="A312">
+        <v>5196580</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" s="2">
-        <v>5191358</v>
+      <c r="A313">
+        <v>5198934</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" s="2">
-        <v>5191299</v>
+      <c r="A314">
+        <v>5198845</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A315" s="2">
-        <v>5191286</v>
+      <c r="A315">
+        <v>5198636</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A316" s="2">
-        <v>5191285</v>
+      <c r="A316">
+        <v>5198634</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A317" s="2">
-        <v>5191283</v>
+      <c r="A317">
+        <v>5198620</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A318" s="2">
-        <v>5191274</v>
+      <c r="A318">
+        <v>5198619</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A319" s="2">
-        <v>5191249</v>
+      <c r="A319">
+        <v>5198519</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A320" s="2">
-        <v>5191222</v>
+      <c r="A320">
+        <v>5198468</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" s="2">
-        <v>5191165</v>
+      <c r="A321">
+        <v>5198449</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A322" s="2">
-        <v>5191151</v>
+      <c r="A322">
+        <v>5198429</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A323" s="2">
-        <v>5191123</v>
+      <c r="A323">
+        <v>5198385</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A324" s="2">
-        <v>5191087</v>
+      <c r="A324">
+        <v>5198350</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A325" s="2">
-        <v>5191081</v>
+      <c r="A325">
+        <v>5198334</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A326" s="2">
-        <v>5191074</v>
+      <c r="A326">
+        <v>5198321</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A327" s="2">
-        <v>5191037</v>
+      <c r="A327">
+        <v>5198315</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A328" s="2">
-        <v>5191025</v>
+      <c r="A328">
+        <v>5198205</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A329" s="2">
-        <v>5192253</v>
+      <c r="A329">
+        <v>5198157</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A330" s="2">
-        <v>5192251</v>
+      <c r="A330">
+        <v>5198113</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A331" s="2">
-        <v>5192213</v>
+      <c r="A331">
+        <v>5198112</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" s="2">
-        <v>5192209</v>
+      <c r="A332">
+        <v>5198078</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A333" s="2">
-        <v>5192144</v>
+      <c r="A333">
+        <v>5197988</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334" s="2">
-        <v>5192126</v>
+      <c r="A334">
+        <v>5197948</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A335" s="2">
-        <v>5192008</v>
+      <c r="A335">
+        <v>5197735</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A336" s="2">
-        <v>5191986</v>
+      <c r="A336">
+        <v>5197733</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A337" s="2">
-        <v>5191946</v>
+      <c r="A337">
+        <v>5197731</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A338" s="2">
-        <v>5191935</v>
+      <c r="A338">
+        <v>5195648</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A339" s="2">
-        <v>5191882</v>
+      <c r="A339">
+        <v>5195624</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340" s="2">
-        <v>5191870</v>
+      <c r="A340">
+        <v>5195413</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341" s="2">
-        <v>5191839</v>
+      <c r="A341">
+        <v>5195322</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" s="2">
-        <v>5191831</v>
+      <c r="A342">
+        <v>5195294</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" s="2">
-        <v>5191783</v>
+      <c r="A343">
+        <v>5195251</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" s="2">
-        <v>5191759</v>
+      <c r="A344">
+        <v>5195244</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A345" s="2">
-        <v>5191740</v>
+      <c r="A345">
+        <v>5195134</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A346" s="2">
-        <v>5191659</v>
+      <c r="A346">
+        <v>5195078</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A347" s="2">
-        <v>5191648</v>
+      <c r="A347">
+        <v>5195051</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A348" s="2">
-        <v>5191607</v>
+      <c r="A348">
+        <v>5195049</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A349" s="2">
-        <v>5197686</v>
+      <c r="A349">
+        <v>5194969</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A350" s="2">
-        <v>5197630</v>
+      <c r="A350">
+        <v>5194955</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A351" s="2">
-        <v>5197374</v>
+      <c r="A351">
+        <v>5194841</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A352" s="2">
-        <v>5197176</v>
+      <c r="A352">
+        <v>5194792</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353" s="2">
-        <v>5197011</v>
+      <c r="A353">
+        <v>5194686</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354" s="2">
-        <v>5197002</v>
+      <c r="A354">
+        <v>5194658</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355" s="2">
-        <v>5196978</v>
+      <c r="A355">
+        <v>5194645</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A356" s="2">
-        <v>5196968</v>
+      <c r="A356">
+        <v>5194620</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A357" s="2">
-        <v>5196911</v>
+      <c r="A357">
+        <v>5194618</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A358" s="2">
-        <v>5196829</v>
+      <c r="A358">
+        <v>5196510</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A359" s="2">
-        <v>5196814</v>
+      <c r="A359">
+        <v>5196411</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A360" s="2">
-        <v>5196772</v>
+      <c r="A360">
+        <v>5196404</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A361" s="2">
-        <v>5196765</v>
+      <c r="A361">
+        <v>5196363</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A362" s="2">
-        <v>5196763</v>
+      <c r="A362">
+        <v>5196354</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A363" s="2">
-        <v>5196719</v>
+      <c r="A363">
+        <v>5196350</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A364" s="2">
-        <v>5196640</v>
+      <c r="A364">
+        <v>5196347</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A365" s="2">
-        <v>5196628</v>
+      <c r="A365">
+        <v>5196336</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A366" s="2">
-        <v>5196599</v>
+      <c r="A366">
+        <v>5196331</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A367" s="2">
-        <v>5196598</v>
+      <c r="A367">
+        <v>5196328</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A368" s="2">
-        <v>5196580</v>
+      <c r="A368">
+        <v>5196221</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" s="2">
-        <v>5198934</v>
+      <c r="A369">
+        <v>5196183</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A370" s="2">
-        <v>5198845</v>
+      <c r="A370">
+        <v>5196128</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A371" s="2">
-        <v>5198636</v>
+      <c r="A371">
+        <v>5196065</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A372" s="2">
-        <v>5198634</v>
+      <c r="A372">
+        <v>5196000</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A373" s="2">
-        <v>5198620</v>
+      <c r="A373">
+        <v>5195996</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A374" s="2">
-        <v>5198619</v>
+      <c r="A374">
+        <v>5195991</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A375" s="2">
-        <v>5198519</v>
+      <c r="A375">
+        <v>5195965</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A376" s="2">
-        <v>5198468</v>
+      <c r="A376">
+        <v>5195827</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A377" s="2">
-        <v>5198449</v>
+      <c r="A377">
+        <v>5195793</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A378" s="2">
-        <v>5198429</v>
+      <c r="A378">
+        <v>5195782</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A379" s="2">
-        <v>5198385</v>
+      <c r="A379">
+        <v>5195690</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A380" s="2">
-        <v>5198350</v>
+      <c r="A380">
+        <v>5195687</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A381" s="2">
-        <v>5198334</v>
+      <c r="A381">
+        <v>5185234</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A382" s="2">
-        <v>5198321</v>
+      <c r="A382">
+        <v>5185233</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A383" s="2">
-        <v>5198315</v>
+      <c r="A383">
+        <v>5185317</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A384" s="2">
-        <v>5198205</v>
+      <c r="A384">
+        <v>5185113</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A385" s="2">
-        <v>5198157</v>
+      <c r="A385">
+        <v>5185005</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A386" s="2">
-        <v>5198113</v>
+      <c r="A386">
+        <v>5185000</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A387" s="2">
-        <v>5198112</v>
+      <c r="A387">
+        <v>5184978</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A388" s="2">
-        <v>5198078</v>
+      <c r="A388">
+        <v>5184945</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A389" s="2">
-        <v>5197988</v>
+      <c r="A389">
+        <v>5185447</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A390" s="2">
-        <v>5197948</v>
+      <c r="A390">
+        <v>5185533</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A391" s="2">
-        <v>5197735</v>
+      <c r="A391">
+        <v>5185538</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A392" s="2">
-        <v>5197733</v>
+      <c r="A392">
+        <v>5185543</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A393" s="2">
-        <v>5197731</v>
+      <c r="A393">
+        <v>5185579</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A394" s="2">
-        <v>5195648</v>
+      <c r="A394">
+        <v>5185641</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A395" s="2">
-        <v>5195624</v>
+      <c r="A395">
+        <v>5184934</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A396" s="2">
-        <v>5195413</v>
+      <c r="A396">
+        <v>5184813</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A397" s="2">
-        <v>5195322</v>
+      <c r="A397">
+        <v>5184811</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A398" s="2">
-        <v>5195294</v>
+      <c r="A398">
+        <v>5184810</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A399" s="2">
-        <v>5195251</v>
+      <c r="A399">
+        <v>5184755</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A400" s="2">
-        <v>5195244</v>
+      <c r="A400">
+        <v>5184619</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A401" s="2">
-        <v>5195134</v>
+      <c r="A401">
+        <v>5184500</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A402" s="2">
-        <v>5195078</v>
+      <c r="A402">
+        <v>5184432</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A403" s="2">
-        <v>5195051</v>
+      <c r="A403">
+        <v>5184329</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A404" s="2">
-        <v>5195049</v>
+      <c r="A404">
+        <v>5184319</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A405" s="2">
-        <v>5194969</v>
+      <c r="A405">
+        <v>5184274</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A406" s="2">
-        <v>5194955</v>
+      <c r="A406">
+        <v>5184190</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A407" s="2">
-        <v>5194841</v>
+      <c r="A407">
+        <v>5186680</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A408" s="2">
-        <v>5194792</v>
+      <c r="A408">
+        <v>5186647</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A409" s="2">
-        <v>5194686</v>
+      <c r="A409">
+        <v>5186644</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A410" s="2">
-        <v>5194658</v>
+      <c r="A410">
+        <v>5186611</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A411" s="2">
-        <v>5194645</v>
+      <c r="A411">
+        <v>5186590</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A412" s="2">
-        <v>5194620</v>
+      <c r="A412">
+        <v>5186557</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A413" s="2">
-        <v>5194618</v>
+      <c r="A413">
+        <v>5186473</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A414" s="2">
-        <v>5196510</v>
+      <c r="A414">
+        <v>5186462</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A415" s="2">
-        <v>5196411</v>
+      <c r="A415">
+        <v>5186373</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A416" s="2">
-        <v>5196404</v>
+      <c r="A416">
+        <v>5186354</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A417" s="2">
-        <v>5196363</v>
+      <c r="A417">
+        <v>5186333</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A418" s="2">
-        <v>5196354</v>
+      <c r="A418">
+        <v>5186281</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A419" s="2">
-        <v>5196350</v>
+      <c r="A419">
+        <v>5186235</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A420" s="2">
-        <v>5196347</v>
+      <c r="A420">
+        <v>5186109</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A421" s="2">
-        <v>5196336</v>
+      <c r="A421">
+        <v>5186080</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A422" s="2">
-        <v>5196331</v>
+      <c r="A422">
+        <v>5186016</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A423" s="2">
-        <v>5196328</v>
+      <c r="A423">
+        <v>5186014</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A424" s="2">
-        <v>5196221</v>
+      <c r="A424">
+        <v>5185922</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A425" s="2">
-        <v>5196183</v>
+      <c r="A425">
+        <v>5185921</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A426" s="2">
-        <v>5196128</v>
+      <c r="A426">
+        <v>5185898</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A427" s="2">
-        <v>5196065</v>
+      <c r="A427">
+        <v>5185835</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A428" s="2">
-        <v>5196000</v>
+      <c r="A428">
+        <v>5185783</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A429" s="2">
-        <v>5195996</v>
+      <c r="A429">
+        <v>5185722</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A430" s="2">
-        <v>5195991</v>
+      <c r="A430">
+        <v>5185674</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A431" s="2">
-        <v>5195965</v>
+      <c r="A431">
+        <v>5184175</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A432" s="2">
-        <v>5195827</v>
+      <c r="A432">
+        <v>5182144</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A433" s="2">
-        <v>5195793</v>
+      <c r="A433">
+        <v>5181953</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A434" s="2">
-        <v>5195782</v>
+      <c r="A434">
+        <v>5181951</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A435" s="2">
-        <v>5195690</v>
+      <c r="A435">
+        <v>5181875</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A436" s="2">
-        <v>5195687</v>
+      <c r="A436">
+        <v>5181874</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A437" s="2">
-        <v>5185234</v>
+      <c r="A437">
+        <v>5181866</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A438" s="2">
-        <v>5185233</v>
+      <c r="A438">
+        <v>5181745</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A439" s="2">
-        <v>5185317</v>
+      <c r="A439">
+        <v>5181708</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A440" s="2">
-        <v>5185113</v>
+      <c r="A440">
+        <v>5181572</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A441" s="2">
-        <v>5185005</v>
+      <c r="A441">
+        <v>5181443</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A442" s="2">
-        <v>5185000</v>
+      <c r="A442">
+        <v>5181403</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A443" s="2">
-        <v>5184978</v>
+      <c r="A443">
+        <v>5181345</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A444" s="2">
-        <v>5184945</v>
+      <c r="A444">
+        <v>5181328</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A445" s="2">
-        <v>5185447</v>
+      <c r="A445">
+        <v>5181292</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A446" s="2">
-        <v>5185533</v>
+      <c r="A446">
+        <v>5181275</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A447" s="2">
-        <v>5185538</v>
+      <c r="A447">
+        <v>5181256</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A448" s="2">
-        <v>5185543</v>
+      <c r="A448">
+        <v>5180953</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A449" s="2">
-        <v>5185579</v>
+      <c r="A449">
+        <v>5180944</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A450" s="2">
-        <v>5185641</v>
+      <c r="A450">
+        <v>5180877</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A451" s="2">
-        <v>5184934</v>
+      <c r="A451">
+        <v>5184172</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A452" s="2">
-        <v>5184813</v>
+      <c r="A452">
+        <v>5184159</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A453" s="2">
-        <v>5184811</v>
+      <c r="A453">
+        <v>5183971</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A454" s="2">
-        <v>5184810</v>
+      <c r="A454">
+        <v>5183970</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A455" s="2">
-        <v>5184755</v>
+      <c r="A455">
+        <v>5183942</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A456" s="2">
-        <v>5184619</v>
+      <c r="A456">
+        <v>5183932</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A457" s="2">
-        <v>5184500</v>
+      <c r="A457">
+        <v>5183783</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A458" s="2">
-        <v>5184432</v>
+      <c r="A458">
+        <v>5183723</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A459" s="2">
-        <v>5184329</v>
+      <c r="A459">
+        <v>5183578</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A460" s="2">
-        <v>5184319</v>
+      <c r="A460">
+        <v>5183577</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A461" s="2">
-        <v>5184274</v>
+      <c r="A461">
+        <v>5183550</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A462" s="2">
-        <v>5184190</v>
+      <c r="A462">
+        <v>5183543</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A463" s="2">
-        <v>5186680</v>
+      <c r="A463">
+        <v>5183534</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A464" s="2">
-        <v>5186647</v>
+      <c r="A464">
+        <v>5183492</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A465" s="2">
-        <v>5186644</v>
+      <c r="A465">
+        <v>5183441</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A466" s="2">
-        <v>5186611</v>
+      <c r="A466">
+        <v>5183387</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A467" s="2">
-        <v>5186590</v>
+      <c r="A467">
+        <v>5183232</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A468" s="2">
-        <v>5186557</v>
+      <c r="A468">
+        <v>5183177</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A469" s="2">
-        <v>5186473</v>
+      <c r="A469">
+        <v>5183160</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A470" s="2">
-        <v>5186462</v>
+      <c r="A470">
+        <v>5183159</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A471" s="2">
-        <v>5186373</v>
+      <c r="A471">
+        <v>5183101</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A472" s="2">
-        <v>5186354</v>
+      <c r="A472">
+        <v>5182868</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A473" s="2">
-        <v>5186333</v>
+      <c r="A473">
+        <v>5182432</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A474" s="2">
-        <v>5186281</v>
+      <c r="A474">
+        <v>5189960</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A475" s="2">
-        <v>5186235</v>
+      <c r="A475">
+        <v>5189847</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A476" s="2">
-        <v>5186109</v>
+      <c r="A476">
+        <v>5189846</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A477" s="2">
-        <v>5186080</v>
+      <c r="A477">
+        <v>5189840</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A478" s="2">
-        <v>5186016</v>
+      <c r="A478">
+        <v>5189820</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A479" s="2">
-        <v>5186014</v>
+      <c r="A479">
+        <v>5189783</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A480" s="2">
-        <v>5185922</v>
+      <c r="A480">
+        <v>5189530</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A481" s="2">
-        <v>5185921</v>
+      <c r="A481">
+        <v>5189411</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A482" s="2">
-        <v>5185898</v>
+      <c r="A482">
+        <v>5189376</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A483" s="2">
-        <v>5185835</v>
+      <c r="A483">
+        <v>5189364</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A484" s="2">
-        <v>5185783</v>
+      <c r="A484">
+        <v>5189363</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A485" s="2">
-        <v>5185722</v>
+      <c r="A485">
+        <v>5189344</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A486" s="2">
-        <v>5185674</v>
+      <c r="A486">
+        <v>5189342</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A487" s="2">
-        <v>5184175</v>
+      <c r="A487">
+        <v>5189328</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A488" s="2">
-        <v>5182144</v>
+      <c r="A488">
+        <v>5189327</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A489" s="2">
-        <v>5181953</v>
+      <c r="A489">
+        <v>5189297</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A490" s="2">
-        <v>5181951</v>
+      <c r="A490">
+        <v>5188724</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A491" s="2">
-        <v>5181875</v>
+      <c r="A491">
+        <v>5188710</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A492" s="2">
-        <v>5181874</v>
+      <c r="A492">
+        <v>5188709</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A493" s="2">
-        <v>5181866</v>
+      <c r="A493">
+        <v>5188680</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A494" s="2">
-        <v>5181745</v>
+      <c r="A494">
+        <v>5188618</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A495" s="2">
-        <v>5181708</v>
+      <c r="A495">
+        <v>5188586</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A496" s="2">
-        <v>5181572</v>
+      <c r="A496">
+        <v>5191024</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A497" s="2">
-        <v>5181443</v>
+      <c r="A497">
+        <v>5190961</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A498" s="2">
-        <v>5181403</v>
+      <c r="A498">
+        <v>5190925</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A499" s="2">
-        <v>5181345</v>
+      <c r="A499">
+        <v>5190844</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A500" s="2">
-        <v>5181328</v>
+      <c r="A500">
+        <v>5190815</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A501" s="2">
-        <v>5181292</v>
+      <c r="A501">
+        <v>5190811</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A502" s="2">
-        <v>5181275</v>
+      <c r="A502">
+        <v>5190757</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A503" s="2">
-        <v>5181256</v>
+      <c r="A503">
+        <v>5190753</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A504" s="2">
-        <v>5180953</v>
+      <c r="A504">
+        <v>5190741</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A505" s="2">
-        <v>5180944</v>
+      <c r="A505">
+        <v>5190737</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A506" s="2">
-        <v>5180877</v>
+      <c r="A506">
+        <v>5190726</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A507" s="2">
-        <v>5184172</v>
+      <c r="A507">
+        <v>5190706</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A508" s="2">
-        <v>5184159</v>
+      <c r="A508">
+        <v>5190626</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A509" s="2">
-        <v>5183971</v>
+      <c r="A509">
+        <v>5190584</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A510" s="2">
-        <v>5183970</v>
+      <c r="A510">
+        <v>5190543</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A511" s="2">
-        <v>5183942</v>
+      <c r="A511">
+        <v>5190533</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A512" s="2">
-        <v>5183932</v>
+      <c r="A512">
+        <v>5190500</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A513" s="2">
-        <v>5183783</v>
+      <c r="A513">
+        <v>5190417</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A514" s="2">
-        <v>5183723</v>
+      <c r="A514">
+        <v>5190224</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A515" s="2">
-        <v>5183578</v>
+      <c r="A515">
+        <v>5190149</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A516" s="2">
-        <v>5183577</v>
+      <c r="A516">
+        <v>5190146</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A517" s="2">
-        <v>5183550</v>
+      <c r="A517">
+        <v>5190067</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A518" s="2">
-        <v>5183543</v>
+      <c r="A518">
+        <v>5190066</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A519" s="2">
-        <v>5183534</v>
+      <c r="A519">
+        <v>5190028</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A520" s="2">
-        <v>5183492</v>
+      <c r="A520">
+        <v>5189980</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A521" s="2">
-        <v>5183441</v>
+      <c r="A521">
+        <v>5188566</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A522" s="2">
-        <v>5183387</v>
+      <c r="A522">
+        <v>5187376</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A523" s="2">
-        <v>5183232</v>
+      <c r="A523">
+        <v>5187372</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A524" s="2">
-        <v>5183177</v>
+      <c r="A524">
+        <v>5187370</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A525" s="2">
-        <v>5183160</v>
+      <c r="A525">
+        <v>5187334</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A526" s="2">
-        <v>5183159</v>
+      <c r="A526">
+        <v>5187287</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A527" s="2">
-        <v>5183101</v>
+      <c r="A527">
+        <v>5187244</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A528" s="2">
-        <v>5182868</v>
+      <c r="A528">
+        <v>5187226</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A529" s="2">
-        <v>5182432</v>
+      <c r="A529">
+        <v>5187225</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A530" s="2">
-        <v>5189960</v>
+      <c r="A530">
+        <v>5187211</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A531" s="2">
-        <v>5189847</v>
+      <c r="A531">
+        <v>5187148</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A532" s="2">
-        <v>5189846</v>
+      <c r="A532">
+        <v>5187074</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A533" s="2">
-        <v>5189840</v>
+      <c r="A533">
+        <v>5187067</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A534" s="2">
-        <v>5189820</v>
+      <c r="A534">
+        <v>5187049</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A535" s="2">
-        <v>5189783</v>
+      <c r="A535">
+        <v>5186874</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A536" s="2">
-        <v>5189530</v>
+      <c r="A536">
+        <v>5186853</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A537" s="2">
-        <v>5189411</v>
+      <c r="A537">
+        <v>5186788</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A538" s="2">
-        <v>5189376</v>
+      <c r="A538">
+        <v>5186734</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A539" s="2">
-        <v>5189364</v>
+      <c r="A539">
+        <v>5188289</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A540" s="2">
-        <v>5189363</v>
+      <c r="A540">
+        <v>5188230</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A541" s="2">
-        <v>5189344</v>
+      <c r="A541">
+        <v>5188216</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A542" s="2">
-        <v>5189342</v>
+      <c r="A542">
+        <v>5188150</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A543" s="2">
-        <v>5189328</v>
+      <c r="A543">
+        <v>5188148</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A544" s="2">
-        <v>5189327</v>
+      <c r="A544">
+        <v>5188024</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A545" s="2">
-        <v>5189297</v>
+      <c r="A545">
+        <v>5187948</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A546" s="2">
-        <v>5188724</v>
+      <c r="A546">
+        <v>5187947</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A547" s="2">
-        <v>5188710</v>
+      <c r="A547">
+        <v>5187936</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A548" s="2">
-        <v>5188709</v>
+      <c r="A548">
+        <v>5187886</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A549" s="2">
-        <v>5188680</v>
+      <c r="A549">
+        <v>5187876</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A550" s="2">
-        <v>5188618</v>
+      <c r="A550">
+        <v>5187747</v>
       </c>
     </row>
     <row r="551" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A551" s="2">
-        <v>5188586</v>
+      <c r="A551">
+        <v>5187718</v>
       </c>
     </row>
     <row r="552" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A552" s="2">
-        <v>5191024</v>
+      <c r="A552">
+        <v>5187711</v>
       </c>
     </row>
     <row r="553" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A553" s="2">
-        <v>5190961</v>
+      <c r="A553">
+        <v>5187669</v>
       </c>
     </row>
     <row r="554" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A554" s="2">
-        <v>5190925</v>
+      <c r="A554">
+        <v>5187621</v>
       </c>
     </row>
     <row r="555" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A555" s="2">
-        <v>5190844</v>
+      <c r="A555">
+        <v>5187620</v>
       </c>
     </row>
     <row r="556" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A556" s="2">
-        <v>5190815</v>
+      <c r="A556">
+        <v>5187618</v>
       </c>
     </row>
     <row r="557" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A557" s="2">
-        <v>5190811</v>
+      <c r="A557">
+        <v>5187540</v>
       </c>
     </row>
     <row r="558" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A558" s="2">
-        <v>5190757</v>
+      <c r="A558">
+        <v>5187539</v>
       </c>
     </row>
     <row r="559" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A559" s="2">
-        <v>5190753</v>
+      <c r="A559">
+        <v>5187490</v>
       </c>
     </row>
     <row r="560" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A560" s="2">
-        <v>5190741</v>
+      <c r="A560">
+        <v>5187471</v>
       </c>
     </row>
     <row r="561" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A561" s="2">
-        <v>5190737</v>
+      <c r="A561">
+        <v>5187465</v>
       </c>
     </row>
     <row r="562" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A562" s="2">
-        <v>5190726</v>
+      <c r="A562">
+        <v>5191365</v>
       </c>
     </row>
     <row r="563" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A563" s="2">
-        <v>5190706</v>
+      <c r="A563">
+        <v>5192322</v>
       </c>
     </row>
     <row r="564" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A564" s="2">
-        <v>5190626</v>
+      <c r="A564">
+        <v>5192321</v>
       </c>
     </row>
     <row r="565" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A565" s="2">
-        <v>5190584</v>
+      <c r="A565">
+        <v>5191604</v>
       </c>
     </row>
     <row r="566" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A566" s="2">
-        <v>5190543</v>
+      <c r="A566">
+        <v>5191125</v>
       </c>
     </row>
     <row r="567" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A567" s="2">
-        <v>5190533</v>
+      <c r="A567">
+        <v>5197478</v>
       </c>
     </row>
     <row r="568" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A568" s="2">
-        <v>5190500</v>
+      <c r="A568">
+        <v>5194521</v>
       </c>
     </row>
     <row r="569" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A569" s="2">
-        <v>5190417</v>
+      <c r="A569">
+        <v>5190847</v>
       </c>
     </row>
     <row r="570" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A570" s="2">
-        <v>5190224</v>
+      <c r="A570">
+        <v>5190842</v>
       </c>
     </row>
     <row r="571" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A571" s="2">
-        <v>5190149</v>
+      <c r="A571">
+        <v>5190275</v>
       </c>
     </row>
     <row r="572" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A572" s="2">
-        <v>5190146</v>
+      <c r="A572">
+        <v>5186728</v>
       </c>
     </row>
     <row r="573" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A573" s="2">
-        <v>5190067</v>
-      </c>
-    </row>
-    <row r="574" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A574" s="2">
-        <v>5190066</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A575" s="2">
-        <v>5190028</v>
-      </c>
-    </row>
-    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A576" s="2">
-        <v>5189980</v>
-      </c>
-    </row>
-    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A577" s="2">
-        <v>5188566</v>
-      </c>
-    </row>
-    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A578" s="2">
-        <v>5187376</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A579" s="2">
-        <v>5187372</v>
-      </c>
-    </row>
-    <row r="580" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A580" s="2">
-        <v>5187370</v>
-      </c>
-    </row>
-    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A581" s="2">
-        <v>5187334</v>
-      </c>
-    </row>
-    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A582" s="2">
-        <v>5187287</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A583" s="2">
-        <v>5187244</v>
-      </c>
-    </row>
-    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A584" s="2">
-        <v>5187226</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A585" s="2">
-        <v>5187225</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A586" s="2">
-        <v>5187211</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A587" s="2">
-        <v>5187148</v>
-      </c>
-    </row>
-    <row r="588" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A588" s="2">
-        <v>5187074</v>
-      </c>
-    </row>
-    <row r="589" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A589" s="2">
-        <v>5187067</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A590" s="2">
-        <v>5187049</v>
-      </c>
-    </row>
-    <row r="591" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A591" s="2">
-        <v>5186874</v>
-      </c>
-    </row>
-    <row r="592" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A592" s="2">
-        <v>5186853</v>
-      </c>
-    </row>
-    <row r="593" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A593" s="2">
-        <v>5186788</v>
-      </c>
-    </row>
-    <row r="594" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A594" s="2">
-        <v>5186734</v>
-      </c>
-    </row>
-    <row r="595" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A595" s="2">
-        <v>5188289</v>
-      </c>
-    </row>
-    <row r="596" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A596" s="2">
-        <v>5188230</v>
-      </c>
-    </row>
-    <row r="597" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A597" s="2">
-        <v>5188216</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A598" s="2">
-        <v>5188150</v>
-      </c>
-    </row>
-    <row r="599" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A599" s="2">
-        <v>5188148</v>
-      </c>
-    </row>
-    <row r="600" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A600" s="2">
-        <v>5188024</v>
-      </c>
-    </row>
-    <row r="601" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A601" s="2">
-        <v>5187948</v>
-      </c>
-    </row>
-    <row r="602" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A602" s="2">
-        <v>5187947</v>
-      </c>
-    </row>
-    <row r="603" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A603" s="2">
-        <v>5187936</v>
-      </c>
-    </row>
-    <row r="604" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A604" s="2">
-        <v>5187886</v>
-      </c>
-    </row>
-    <row r="605" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A605" s="2">
-        <v>5187876</v>
-      </c>
-    </row>
-    <row r="606" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A606" s="2">
-        <v>5187747</v>
-      </c>
-    </row>
-    <row r="607" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A607" s="2">
-        <v>5187718</v>
-      </c>
-    </row>
-    <row r="608" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A608" s="2">
-        <v>5187711</v>
-      </c>
-    </row>
-    <row r="609" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A609" s="2">
-        <v>5187669</v>
-      </c>
-    </row>
-    <row r="610" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A610" s="2">
-        <v>5187621</v>
-      </c>
-    </row>
-    <row r="611" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A611" s="2">
-        <v>5187620</v>
-      </c>
-    </row>
-    <row r="612" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A612" s="2">
-        <v>5187618</v>
-      </c>
-    </row>
-    <row r="613" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A613" s="2">
-        <v>5187540</v>
-      </c>
-    </row>
-    <row r="614" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A614" s="2">
-        <v>5187539</v>
-      </c>
-    </row>
-    <row r="615" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A615" s="2">
-        <v>5187490</v>
-      </c>
-    </row>
-    <row r="616" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A616" s="2">
-        <v>5187471</v>
-      </c>
-    </row>
-    <row r="617" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A617" s="2">
-        <v>5187465</v>
-      </c>
-    </row>
-    <row r="618" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A618" s="2">
-        <v>5191365</v>
-      </c>
-    </row>
-    <row r="619" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A619" s="2">
-        <v>5192322</v>
-      </c>
-    </row>
-    <row r="620" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A620" s="2">
-        <v>5192321</v>
-      </c>
-    </row>
-    <row r="621" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A621" s="2">
-        <v>5191604</v>
-      </c>
-    </row>
-    <row r="622" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A622" s="2">
-        <v>5191125</v>
-      </c>
-    </row>
-    <row r="623" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A623" s="2">
-        <v>5197478</v>
-      </c>
-    </row>
-    <row r="624" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A624" s="2">
-        <v>5194521</v>
-      </c>
-    </row>
-    <row r="625" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A625" s="2">
-        <v>5190847</v>
-      </c>
-    </row>
-    <row r="626" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A626" s="2">
-        <v>5190842</v>
-      </c>
-    </row>
-    <row r="627" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A627" s="2">
-        <v>5190275</v>
-      </c>
-    </row>
-    <row r="628" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A628" s="2">
-        <v>5186728</v>
-      </c>
-    </row>
-    <row r="629" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A629" s="2">
+      <c r="A573">
         <v>5186695</v>
       </c>
     </row>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0430BA87-B1BF-4DF1-BAD4-77EB3BEFAE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9383B88D-F666-4967-A460-EB55C321C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>OM</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Ordem pendente!</t>
   </si>
 </sst>
 </file>
@@ -388,11 +391,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B481"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -405,2861 +408,2404 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5197256</v>
+        <v>5187222</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5197032</v>
+        <v>5187166</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5197031</v>
+        <v>5187149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5196998</v>
+        <v>5186850</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5196890</v>
+        <v>5188463</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5196715</v>
+        <v>5188355</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5196605</v>
+        <v>5188319</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>5196602</v>
+        <v>5188255</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5198949</v>
+        <v>5188198</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5198837</v>
+        <v>5188192</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5198756</v>
+        <v>5187953</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5198577</v>
+        <v>5187877</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5198523</v>
+        <v>5187759</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5198431</v>
+        <v>5187619</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5198369</v>
+        <v>5187585</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5197989</v>
+        <v>5187538</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5196541</v>
+        <v>5187537</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5195611</v>
+        <v>5192968</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5195435</v>
+        <v>5192651</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5195416</v>
+        <v>5192401</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5195415</v>
+        <v>5192313</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5195359</v>
+        <v>5197502</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>5195296</v>
+        <v>5194650</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>5195285</v>
+        <v>5185481</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>5195117</v>
+        <v>5181121</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5194533</v>
+        <v>5183699</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5196450</v>
+        <v>5188728</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5196443</v>
+        <v>5188721</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5196405</v>
+        <v>5192448</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>5196349</v>
+        <v>5194809</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5196341</v>
+        <v>5187048</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5196334</v>
+        <v>5190918</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5196240</v>
+        <v>5192492</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5195998</v>
+        <v>5192406</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5195967</v>
+        <v>5192399</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>5195957</v>
+        <v>5194277</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5195791</v>
+        <v>5193851</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>5185446</v>
+        <v>5193720</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>5185530</v>
+        <v>5191414</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>5185595</v>
+        <v>5191345</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>5184871</v>
+        <v>5197373</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5184818</v>
+        <v>5197368</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>5184507</v>
+        <v>5197166</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>5184340</v>
+        <v>5197104</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>5184327</v>
+        <v>5196542</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>5184283</v>
+        <v>5198889</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>5184282</v>
+        <v>5198540</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>5186538</v>
+        <v>5198145</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>5186492</v>
+        <v>5197990</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>5186403</v>
+        <v>5197820</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>5186177</v>
+        <v>5195596</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>5185939</v>
+        <v>5195261</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>5185897</v>
+        <v>5195162</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>5185746</v>
+        <v>5194878</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>5182386</v>
+        <v>5194821</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>5182296</v>
+        <v>5194720</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>5181876</v>
+        <v>5196413</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>5181792</v>
+        <v>5196218</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>5181703</v>
+        <v>5195864</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>5181670</v>
+        <v>5195787</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>5181437</v>
+        <v>5195659</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>5180981</v>
+        <v>5185573</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5180925</v>
+        <v>5184883</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>5184123</v>
+        <v>5186358</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>5183689</v>
+        <v>5186352</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>5183684</v>
+        <v>5186311</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>5183552</v>
+        <v>5186171</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>5183330</v>
+        <v>5186100</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>5183238</v>
+        <v>5185954</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>5183237</v>
+        <v>5185754</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>5183122</v>
+        <v>5182405</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>5183092</v>
+        <v>5181728</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>5182769</v>
+        <v>5181433</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>5189780</v>
+        <v>5181427</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>5189722</v>
+        <v>5181232</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>5189662</v>
+        <v>5180876</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>5189652</v>
+        <v>5183454</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>5189520</v>
+        <v>5182872</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>5189515</v>
+        <v>5182832</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>5189413</v>
+        <v>5182762</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>5189032</v>
+        <v>5189808</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>5188868</v>
+        <v>5189663</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>5188841</v>
+        <v>5188809</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>5190831</v>
+        <v>5188704</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>5190655</v>
+        <v>5188662</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>5190614</v>
+        <v>5190913</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>5190444</v>
+        <v>5190908</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>5190065</v>
+        <v>5190705</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>5190038</v>
+        <v>5190267</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>5187421</v>
+        <v>5187444</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>5187361</v>
+        <v>5187336</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>5187232</v>
+        <v>5187326</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>5187222</v>
+        <v>5187253</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>5187166</v>
+        <v>5187208</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>5187149</v>
+        <v>5187151</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>5186850</v>
+        <v>5187010</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>5188463</v>
+        <v>5187007</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>5188355</v>
+        <v>5186866</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>5188319</v>
+        <v>5186864</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>5188255</v>
+        <v>5188362</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>5188198</v>
+        <v>5187954</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>5188192</v>
+        <v>5197600</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>5187953</v>
+        <v>5182053</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>5187877</v>
+        <v>5181608</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>5187759</v>
+        <v>5181432</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>5187619</v>
+        <v>5181431</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>5187585</v>
+        <v>5182601</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>5187538</v>
+        <v>5186949</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>5187537</v>
+        <v>5186872</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>5192968</v>
+        <v>5188028</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>5192651</v>
+        <v>5198573</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>5192401</v>
+        <v>5186010</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>5192313</v>
+        <v>5192919</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>5197502</v>
+        <v>5192915</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>5194650</v>
+        <v>5192920</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>5185481</v>
+        <v>5192914</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>5181121</v>
+        <v>5192841</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>5183699</v>
+        <v>5192828</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>5188728</v>
+        <v>5192949</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>5188721</v>
+        <v>5192952</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>5192448</v>
+        <v>5192973</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>5194809</v>
+        <v>5192975</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>5187048</v>
+        <v>5192998</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>5190918</v>
+        <v>5192795</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>5192492</v>
+        <v>5192793</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>5192406</v>
+        <v>5192789</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>5192399</v>
+        <v>5192404</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>5194277</v>
+        <v>5192400</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>5193851</v>
+        <v>5194404</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>5193720</v>
+        <v>5194343</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>5191414</v>
+        <v>5194280</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>5191345</v>
+        <v>5194245</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>5197373</v>
+        <v>5194244</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>5197368</v>
+        <v>5194243</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>5197166</v>
+        <v>5194147</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>5197104</v>
+        <v>5194067</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>5196542</v>
+        <v>5193929</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>5198889</v>
+        <v>5193837</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>5198540</v>
+        <v>5193789</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>5198145</v>
+        <v>5193786</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>5197990</v>
+        <v>5193663</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>5197820</v>
+        <v>5193494</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>5195596</v>
+        <v>5193409</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>5195261</v>
+        <v>5193387</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>5195162</v>
+        <v>5193385</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>5194878</v>
+        <v>5193363</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>5194821</v>
+        <v>5193352</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>5194720</v>
+        <v>5193320</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>5196413</v>
+        <v>5193288</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>5196218</v>
+        <v>5193287</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>5195864</v>
+        <v>5193247</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>5195787</v>
+        <v>5193226</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>5195659</v>
+        <v>5193177</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>5185573</v>
+        <v>5193090</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>5184883</v>
+        <v>5191531</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>5186358</v>
+        <v>5191522</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>5186352</v>
+        <v>5191497</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>5186311</v>
+        <v>5191494</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>5186171</v>
+        <v>5191420</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>5186100</v>
+        <v>5191413</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>5185954</v>
+        <v>5191411</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>5185754</v>
+        <v>5191410</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>5182405</v>
+        <v>5191364</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>5181728</v>
+        <v>5191358</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>5181433</v>
+        <v>5191299</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>5181427</v>
+        <v>5191286</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>5181232</v>
+        <v>5191285</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>5180876</v>
+        <v>5191283</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>5183454</v>
+        <v>5191274</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>5182872</v>
+        <v>5191249</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>5182832</v>
+        <v>5191222</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>5182762</v>
+        <v>5191165</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>5189808</v>
+        <v>5191151</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>5189663</v>
+        <v>5191123</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>5188809</v>
+        <v>5191087</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>5188704</v>
+        <v>5191081</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>5188662</v>
+        <v>5191074</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>5190913</v>
+        <v>5191037</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>5190908</v>
+        <v>5191025</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>5190705</v>
+        <v>5192253</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>5190267</v>
+        <v>5192251</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>5187444</v>
+        <v>5192213</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>5187336</v>
+        <v>5192209</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>5187326</v>
+        <v>5192144</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>5187253</v>
+        <v>5192126</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>5187208</v>
+        <v>5192008</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>5187151</v>
+        <v>5191986</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>5187010</v>
+        <v>5191946</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>5187007</v>
+        <v>5191935</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>5186866</v>
+        <v>5191882</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>5186864</v>
+        <v>5191870</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>5188362</v>
+        <v>5191839</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>5187954</v>
+        <v>5191831</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>5197600</v>
+        <v>5191783</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>5182053</v>
+        <v>5191759</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>5181608</v>
+        <v>5191740</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>5181432</v>
+        <v>5191659</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>5181431</v>
+        <v>5191648</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>5182601</v>
+        <v>5191607</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>5186949</v>
+        <v>5197686</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>5186872</v>
+        <v>5197630</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>5188028</v>
+        <v>5197374</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>5198573</v>
+        <v>5197176</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>5186010</v>
+        <v>5197011</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>5192919</v>
+        <v>5197002</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>5192915</v>
+        <v>5196978</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>5192920</v>
+        <v>5196968</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>5192914</v>
+        <v>5196911</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>5192841</v>
+        <v>5196829</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>5192828</v>
+        <v>5196814</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>5192949</v>
+        <v>5196772</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>5192952</v>
+        <v>5196765</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>5192973</v>
+        <v>5196763</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>5192975</v>
+        <v>5196719</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>5192998</v>
+        <v>5196640</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>5192795</v>
+        <v>5196628</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>5192793</v>
+        <v>5196599</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>5192789</v>
+        <v>5196598</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>5192404</v>
+        <v>5196580</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>5192400</v>
+        <v>5198934</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>5194404</v>
+        <v>5198845</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>5194343</v>
+        <v>5198636</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>5194280</v>
+        <v>5198634</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>5194245</v>
+        <v>5198620</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>5194244</v>
+        <v>5198619</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>5194243</v>
+        <v>5198519</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>5194147</v>
+        <v>5198468</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>5194067</v>
+        <v>5198449</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>5193929</v>
+        <v>5198429</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>5193837</v>
+        <v>5198385</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>5193789</v>
+        <v>5198350</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>5193786</v>
+        <v>5198334</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>5193663</v>
+        <v>5198321</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>5193494</v>
+        <v>5198315</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>5193409</v>
+        <v>5198205</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>5193387</v>
+        <v>5198157</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>5193385</v>
+        <v>5198113</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>5193363</v>
+        <v>5198112</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>5193352</v>
+        <v>5198078</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>5193320</v>
+        <v>5197988</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>5193288</v>
+        <v>5197948</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>5193287</v>
+        <v>5197735</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>5193247</v>
+        <v>5197733</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>5193226</v>
+        <v>5197731</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>5193177</v>
+        <v>5195648</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>5193090</v>
+        <v>5195624</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>5191531</v>
+        <v>5195413</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>5191522</v>
+        <v>5195322</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>5191497</v>
+        <v>5195294</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>5191494</v>
+        <v>5195251</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>5191420</v>
+        <v>5195244</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>5191413</v>
+        <v>5195134</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>5191411</v>
+        <v>5195078</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>5191410</v>
+        <v>5195051</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>5191364</v>
+        <v>5195049</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>5191358</v>
+        <v>5194969</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>5191299</v>
+        <v>5194955</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>5191286</v>
+        <v>5194841</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>5191285</v>
+        <v>5194792</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>5191283</v>
+        <v>5194686</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>5191274</v>
+        <v>5194658</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>5191249</v>
+        <v>5194645</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>5191222</v>
+        <v>5194620</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>5191165</v>
+        <v>5194618</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>5191151</v>
+        <v>5196510</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>5191123</v>
+        <v>5196411</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>5191087</v>
+        <v>5196404</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>5191081</v>
+        <v>5196363</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>5191074</v>
+        <v>5196354</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>5191037</v>
+        <v>5196350</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>5191025</v>
+        <v>5196347</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>5192253</v>
+        <v>5196336</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>5192251</v>
+        <v>5196331</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>5192213</v>
+        <v>5196328</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>5192209</v>
+        <v>5196221</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>5192144</v>
+        <v>5196183</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>5192126</v>
+        <v>5196128</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>5192008</v>
+        <v>5196065</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>5191986</v>
+        <v>5196000</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>5191946</v>
+        <v>5195996</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>5191935</v>
+        <v>5195991</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>5191882</v>
+        <v>5195965</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>5191870</v>
+        <v>5195827</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>5191839</v>
+        <v>5195793</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>5191831</v>
+        <v>5195782</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>5191783</v>
+        <v>5195690</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>5191759</v>
+        <v>5195687</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>5191740</v>
+        <v>5185234</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>5191659</v>
+        <v>5185233</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>5191648</v>
+        <v>5185317</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>5191607</v>
+        <v>5185113</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>5197686</v>
+        <v>5185005</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>5197630</v>
+        <v>5185000</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>5197374</v>
+        <v>5184978</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>5197176</v>
+        <v>5184945</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>5197011</v>
+        <v>5185447</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>5197002</v>
+        <v>5185533</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>5196978</v>
+        <v>5185538</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>5196968</v>
+        <v>5185543</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>5196911</v>
+        <v>5185579</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>5196829</v>
+        <v>5185641</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>5196814</v>
+        <v>5184934</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>5196772</v>
+        <v>5184813</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>5196765</v>
+        <v>5184811</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>5196763</v>
+        <v>5184810</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>5196719</v>
+        <v>5184755</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>5196640</v>
+        <v>5184619</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>5196628</v>
+        <v>5184500</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>5196599</v>
+        <v>5184432</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>5196598</v>
+        <v>5184329</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>5196580</v>
+        <v>5184319</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>5198934</v>
+        <v>5184274</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>5198845</v>
+        <v>5184190</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>5198636</v>
+        <v>5186680</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>5198634</v>
+        <v>5186647</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>5198620</v>
+        <v>5186644</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>5198619</v>
+        <v>5186611</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>5198519</v>
+        <v>5186590</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>5198468</v>
+        <v>5186557</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>5198449</v>
+        <v>5186473</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>5198429</v>
+        <v>5186462</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>5198385</v>
+        <v>5186373</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>5198350</v>
+        <v>5186354</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>5198334</v>
+        <v>5186333</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>5198321</v>
+        <v>5186281</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>5198315</v>
+        <v>5186235</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>5198205</v>
+        <v>5186109</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>5198157</v>
+        <v>5186080</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>5198113</v>
+        <v>5186016</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>5198112</v>
+        <v>5186014</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>5198078</v>
+        <v>5185922</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>5197988</v>
+        <v>5185921</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>5197948</v>
+        <v>5185898</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>5197735</v>
+        <v>5185835</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>5197733</v>
+        <v>5185783</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>5197731</v>
+        <v>5185722</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>5195648</v>
+        <v>5185674</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>5195624</v>
+        <v>5184175</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>5195413</v>
+        <v>5182144</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>5195322</v>
+        <v>5181953</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>5195294</v>
+        <v>5181951</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>5195251</v>
+        <v>5181875</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>5195244</v>
+        <v>5181874</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>5195134</v>
+        <v>5181866</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>5195078</v>
+        <v>5181745</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>5195051</v>
+        <v>5181708</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>5195049</v>
+        <v>5181572</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>5194969</v>
+        <v>5181443</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>5194955</v>
+        <v>5181403</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>5194841</v>
+        <v>5181345</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>5194792</v>
+        <v>5181328</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>5194686</v>
+        <v>5181292</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>5194658</v>
+        <v>5181275</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>5194645</v>
+        <v>5181256</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>5194620</v>
+        <v>5180953</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>5194618</v>
+        <v>5180944</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>5196510</v>
+        <v>5180877</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>5196411</v>
+        <v>5184172</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>5196404</v>
+        <v>5184159</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>5196363</v>
+        <v>5183971</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>5196354</v>
+        <v>5183970</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>5196350</v>
+        <v>5183942</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>5196347</v>
+        <v>5183932</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>5196336</v>
+        <v>5183783</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>5196331</v>
+        <v>5183723</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>5196328</v>
+        <v>5183578</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>5196221</v>
+        <v>5183577</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>5196183</v>
+        <v>5183550</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>5196128</v>
+        <v>5183543</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371">
-        <v>5196065</v>
+        <v>5183534</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372">
-        <v>5196000</v>
+        <v>5183492</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373">
-        <v>5195996</v>
+        <v>5183441</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374">
-        <v>5195991</v>
+        <v>5183387</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375">
-        <v>5195965</v>
+        <v>5183232</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376">
-        <v>5195827</v>
+        <v>5183177</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377">
-        <v>5195793</v>
+        <v>5183160</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>5195782</v>
+        <v>5183159</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>5195690</v>
+        <v>5183101</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>5195687</v>
+        <v>5182868</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>5185234</v>
+        <v>5182432</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>5185233</v>
+        <v>5189960</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>5185317</v>
+        <v>5189847</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>5185113</v>
+        <v>5189846</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>5185005</v>
+        <v>5189840</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>5185000</v>
+        <v>5189820</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387">
-        <v>5184978</v>
+        <v>5189783</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388">
-        <v>5184945</v>
+        <v>5189530</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389">
-        <v>5185447</v>
+        <v>5189411</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390">
-        <v>5185533</v>
+        <v>5189376</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391">
-        <v>5185538</v>
+        <v>5189364</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392">
-        <v>5185543</v>
+        <v>5189363</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393">
-        <v>5185579</v>
+        <v>5189344</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394">
-        <v>5185641</v>
+        <v>5189342</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395">
-        <v>5184934</v>
+        <v>5189328</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>5184813</v>
+        <v>5189327</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>5184811</v>
+        <v>5189297</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>5184810</v>
+        <v>5188724</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>5184755</v>
+        <v>5188710</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>5184619</v>
+        <v>5188709</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>5184500</v>
+        <v>5188680</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>5184432</v>
+        <v>5188618</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>5184329</v>
+        <v>5188586</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>5184319</v>
+        <v>5191024</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>5184274</v>
+        <v>5190961</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>5184190</v>
+        <v>5190925</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>5186680</v>
+        <v>5190844</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>5186647</v>
+        <v>5190815</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>5186644</v>
+        <v>5190811</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>5186611</v>
+        <v>5190757</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>5186590</v>
+        <v>5190753</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>5186557</v>
+        <v>5190741</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>5186473</v>
+        <v>5190737</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>5186462</v>
+        <v>5190726</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>5186373</v>
+        <v>5190706</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>5186354</v>
+        <v>5190626</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>5186333</v>
+        <v>5190584</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>5186281</v>
+        <v>5190543</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A419">
-        <v>5186235</v>
+        <v>5190533</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>5186109</v>
+        <v>5190500</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>5186080</v>
+        <v>5190417</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>5186016</v>
+        <v>5190224</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>5186014</v>
+        <v>5190149</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>5185922</v>
+        <v>5190146</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>5185921</v>
+        <v>5190067</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>5185898</v>
+        <v>5190066</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>5185835</v>
+        <v>5190028</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>5185783</v>
+        <v>5189980</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>5185722</v>
+        <v>5188566</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>5185674</v>
+        <v>5187376</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>5184175</v>
+        <v>5187372</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>5182144</v>
+        <v>5187370</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>5181953</v>
+        <v>5187334</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>5181951</v>
+        <v>5187287</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>5181875</v>
+        <v>5187244</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>5181874</v>
+        <v>5187226</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>5181866</v>
+        <v>5187225</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>5181745</v>
+        <v>5187211</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>5181708</v>
+        <v>5187148</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>5181572</v>
+        <v>5187074</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>5181443</v>
+        <v>5187067</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>5181403</v>
+        <v>5187049</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>5181345</v>
+        <v>5186874</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>5181328</v>
+        <v>5186853</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>5181292</v>
+        <v>5186788</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>5181275</v>
+        <v>5186734</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>5181256</v>
+        <v>5188289</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>5180953</v>
+        <v>5188230</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>5180944</v>
+        <v>5188216</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>5180877</v>
+        <v>5188150</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>5184172</v>
+        <v>5188148</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>5184159</v>
+        <v>5188024</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>5183971</v>
+        <v>5187948</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>5183970</v>
+        <v>5187947</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A455">
-        <v>5183942</v>
+        <v>5187936</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A456">
-        <v>5183932</v>
+        <v>5187886</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A457">
-        <v>5183783</v>
+        <v>5187876</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A458">
-        <v>5183723</v>
+        <v>5187747</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A459">
-        <v>5183578</v>
+        <v>5187718</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A460">
-        <v>5183577</v>
+        <v>5187711</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A461">
-        <v>5183550</v>
+        <v>5187669</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>5183543</v>
+        <v>5187621</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>5183534</v>
+        <v>5187620</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>5183492</v>
+        <v>5187618</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>5183441</v>
+        <v>5187540</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>5183387</v>
+        <v>5187539</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>5183232</v>
+        <v>5187490</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>5183177</v>
+        <v>5187471</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>5183160</v>
+        <v>5187465</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A470">
-        <v>5183159</v>
+        <v>5191365</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A471">
-        <v>5183101</v>
+        <v>5192322</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A472">
-        <v>5182868</v>
+        <v>5192321</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A473">
-        <v>5182432</v>
+        <v>5191604</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A474">
-        <v>5189960</v>
+        <v>5191125</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A475">
-        <v>5189847</v>
+        <v>5197478</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A476">
-        <v>5189846</v>
+        <v>5194521</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A477">
-        <v>5189840</v>
+        <v>5190847</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A478">
-        <v>5189820</v>
+        <v>5190842</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A479">
-        <v>5189783</v>
+        <v>5190275</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A480">
-        <v>5189530</v>
+        <v>5186728</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A481">
-        <v>5189411</v>
-      </c>
-    </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A482">
-        <v>5189376</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A483">
-        <v>5189364</v>
-      </c>
-    </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A484">
-        <v>5189363</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A485">
-        <v>5189344</v>
-      </c>
-    </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A486">
-        <v>5189342</v>
-      </c>
-    </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A487">
-        <v>5189328</v>
-      </c>
-    </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A488">
-        <v>5189327</v>
-      </c>
-    </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A489">
-        <v>5189297</v>
-      </c>
-    </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A490">
-        <v>5188724</v>
-      </c>
-    </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A491">
-        <v>5188710</v>
-      </c>
-    </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A492">
-        <v>5188709</v>
-      </c>
-    </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A493">
-        <v>5188680</v>
-      </c>
-    </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A494">
-        <v>5188618</v>
-      </c>
-    </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A495">
-        <v>5188586</v>
-      </c>
-    </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A496">
-        <v>5191024</v>
-      </c>
-    </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A497">
-        <v>5190961</v>
-      </c>
-    </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A498">
-        <v>5190925</v>
-      </c>
-    </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A499">
-        <v>5190844</v>
-      </c>
-    </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A500">
-        <v>5190815</v>
-      </c>
-    </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A501">
-        <v>5190811</v>
-      </c>
-    </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A502">
-        <v>5190757</v>
-      </c>
-    </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A503">
-        <v>5190753</v>
-      </c>
-    </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A504">
-        <v>5190741</v>
-      </c>
-    </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A505">
-        <v>5190737</v>
-      </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A506">
-        <v>5190726</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A507">
-        <v>5190706</v>
-      </c>
-    </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A508">
-        <v>5190626</v>
-      </c>
-    </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A509">
-        <v>5190584</v>
-      </c>
-    </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A510">
-        <v>5190543</v>
-      </c>
-    </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A511">
-        <v>5190533</v>
-      </c>
-    </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A512">
-        <v>5190500</v>
-      </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A513">
-        <v>5190417</v>
-      </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A514">
-        <v>5190224</v>
-      </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A515">
-        <v>5190149</v>
-      </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A516">
-        <v>5190146</v>
-      </c>
-    </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A517">
-        <v>5190067</v>
-      </c>
-    </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A518">
-        <v>5190066</v>
-      </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A519">
-        <v>5190028</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A520">
-        <v>5189980</v>
-      </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A521">
-        <v>5188566</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A522">
-        <v>5187376</v>
-      </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A523">
-        <v>5187372</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A524">
-        <v>5187370</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A525">
-        <v>5187334</v>
-      </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A526">
-        <v>5187287</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A527">
-        <v>5187244</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A528">
-        <v>5187226</v>
-      </c>
-    </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A529">
-        <v>5187225</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A530">
-        <v>5187211</v>
-      </c>
-    </row>
-    <row r="531" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A531">
-        <v>5187148</v>
-      </c>
-    </row>
-    <row r="532" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A532">
-        <v>5187074</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A533">
-        <v>5187067</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A534">
-        <v>5187049</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A535">
-        <v>5186874</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A536">
-        <v>5186853</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A537">
-        <v>5186788</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A538">
-        <v>5186734</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A539">
-        <v>5188289</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A540">
-        <v>5188230</v>
-      </c>
-    </row>
-    <row r="541" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A541">
-        <v>5188216</v>
-      </c>
-    </row>
-    <row r="542" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A542">
-        <v>5188150</v>
-      </c>
-    </row>
-    <row r="543" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A543">
-        <v>5188148</v>
-      </c>
-    </row>
-    <row r="544" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A544">
-        <v>5188024</v>
-      </c>
-    </row>
-    <row r="545" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A545">
-        <v>5187948</v>
-      </c>
-    </row>
-    <row r="546" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A546">
-        <v>5187947</v>
-      </c>
-    </row>
-    <row r="547" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A547">
-        <v>5187936</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A548">
-        <v>5187886</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A549">
-        <v>5187876</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A550">
-        <v>5187747</v>
-      </c>
-    </row>
-    <row r="551" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A551">
-        <v>5187718</v>
-      </c>
-    </row>
-    <row r="552" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A552">
-        <v>5187711</v>
-      </c>
-    </row>
-    <row r="553" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A553">
-        <v>5187669</v>
-      </c>
-    </row>
-    <row r="554" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A554">
-        <v>5187621</v>
-      </c>
-    </row>
-    <row r="555" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A555">
-        <v>5187620</v>
-      </c>
-    </row>
-    <row r="556" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A556">
-        <v>5187618</v>
-      </c>
-    </row>
-    <row r="557" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A557">
-        <v>5187540</v>
-      </c>
-    </row>
-    <row r="558" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A558">
-        <v>5187539</v>
-      </c>
-    </row>
-    <row r="559" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A559">
-        <v>5187490</v>
-      </c>
-    </row>
-    <row r="560" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A560">
-        <v>5187471</v>
-      </c>
-    </row>
-    <row r="561" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A561">
-        <v>5187465</v>
-      </c>
-    </row>
-    <row r="562" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A562">
-        <v>5191365</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A563">
-        <v>5192322</v>
-      </c>
-    </row>
-    <row r="564" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A564">
-        <v>5192321</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A565">
-        <v>5191604</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A566">
-        <v>5191125</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A567">
-        <v>5197478</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A568">
-        <v>5194521</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A569">
-        <v>5190847</v>
-      </c>
-    </row>
-    <row r="570" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A570">
-        <v>5190842</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A571">
-        <v>5190275</v>
-      </c>
-    </row>
-    <row r="572" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A572">
-        <v>5186728</v>
-      </c>
-    </row>
-    <row r="573" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A573">
         <v>5186695</v>
       </c>
     </row>

--- a/Open-OMs.xlsx
+++ b/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E3FBC8-BA82-4220-A79F-231DB4FEC50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20F7D05-CB1D-41F1-94C4-F1A7E91DE39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>OM</t>
   </si>
@@ -28,7 +28,187 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Ordem pendente!</t>
+    <t>5201140</t>
+  </si>
+  <si>
+    <t>5202346</t>
+  </si>
+  <si>
+    <t>5202256</t>
+  </si>
+  <si>
+    <t>5202085</t>
+  </si>
+  <si>
+    <t>5202363</t>
+  </si>
+  <si>
+    <t>5202429</t>
+  </si>
+  <si>
+    <t>5202238</t>
+  </si>
+  <si>
+    <t>5201910</t>
+  </si>
+  <si>
+    <t>5202158</t>
+  </si>
+  <si>
+    <t>5202285</t>
+  </si>
+  <si>
+    <t>5199416</t>
+  </si>
+  <si>
+    <t>5201841</t>
+  </si>
+  <si>
+    <t>5202020</t>
+  </si>
+  <si>
+    <t>5202149</t>
+  </si>
+  <si>
+    <t>685601384991</t>
+  </si>
+  <si>
+    <t>685601402315</t>
+  </si>
+  <si>
+    <t>685601402768</t>
+  </si>
+  <si>
+    <t>685601409515</t>
+  </si>
+  <si>
+    <t>685601400376</t>
+  </si>
+  <si>
+    <t>685601399941</t>
+  </si>
+  <si>
+    <t>685601403274</t>
+  </si>
+  <si>
+    <t>685601411519</t>
+  </si>
+  <si>
+    <t>5200588</t>
+  </si>
+  <si>
+    <t>5201908</t>
+  </si>
+  <si>
+    <t>5201823</t>
+  </si>
+  <si>
+    <t>5201825</t>
+  </si>
+  <si>
+    <t>5201259</t>
+  </si>
+  <si>
+    <t>5200496</t>
+  </si>
+  <si>
+    <t>5201168</t>
+  </si>
+  <si>
+    <t>5201173</t>
+  </si>
+  <si>
+    <t>685601377951</t>
+  </si>
+  <si>
+    <t>685601403631</t>
+  </si>
+  <si>
+    <t>685601403633</t>
+  </si>
+  <si>
+    <t>685601406671</t>
+  </si>
+  <si>
+    <t>685601399661</t>
+  </si>
+  <si>
+    <t>685601398112</t>
+  </si>
+  <si>
+    <t>685601396397</t>
+  </si>
+  <si>
+    <t>685601399939</t>
+  </si>
+  <si>
+    <t>685601400296</t>
+  </si>
+  <si>
+    <t>685601400710</t>
+  </si>
+  <si>
+    <t>685601401439</t>
+  </si>
+  <si>
+    <t>685601402766</t>
+  </si>
+  <si>
+    <t>685601407005</t>
+  </si>
+  <si>
+    <t>685601407007</t>
+  </si>
+  <si>
+    <t>5202261</t>
+  </si>
+  <si>
+    <t>5201426</t>
+  </si>
+  <si>
+    <t>5202021</t>
+  </si>
+  <si>
+    <t>5202092</t>
+  </si>
+  <si>
+    <t>5202178</t>
+  </si>
+  <si>
+    <t>5202181</t>
+  </si>
+  <si>
+    <t>5200465</t>
+  </si>
+  <si>
+    <t>5200626</t>
+  </si>
+  <si>
+    <t>5200817</t>
+  </si>
+  <si>
+    <t>5201529</t>
+  </si>
+  <si>
+    <t>5200619</t>
+  </si>
+  <si>
+    <t>685601389525</t>
+  </si>
+  <si>
+    <t>685601390371</t>
+  </si>
+  <si>
+    <t>685601400030</t>
+  </si>
+  <si>
+    <t>685601403917</t>
+  </si>
+  <si>
+    <t>685601409281</t>
+  </si>
+  <si>
+    <t>685601409528</t>
   </si>
 </sst>
 </file>
@@ -84,9 +264,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -391,15 +577,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -407,19 +593,388 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>5187222</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5198573</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>5201341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>5201401</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>5201122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>5200867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>5201142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>5200639</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>5200500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>5198992</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>685601409344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>685601408192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>685601400820</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>685601380912</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>685601404560</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>685601408234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>685601402087</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>685601408457</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
